--- a/Config/Datas/Tables/g_怪物_MonsterConfig.xlsx
+++ b/Config/Datas/Tables/g_怪物_MonsterConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbMonster" sheetId="1" r:id="R9cc1342ace6e4819"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbMonster" sheetId="1" r:id="Rb3065af57bad48f5"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -16,7 +16,7 @@
   <x:numFmts count="1">
     <x:numFmt numFmtId="200" formatCode="0"/>
   </x:numFmts>
-  <x:fonts count="8">
+  <x:fonts count="13">
     <x:font>
       <x:sz val="11"/>
       <x:name val="Carlito"/>
@@ -62,8 +62,35 @@
       <x:color rgb="FFFFFFFF"/>
       <x:name val="Arial"/>
     </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:color rgb="FF334155"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FF17365D"/>
+      <x:name val="Microsoft YaHei"/>
+    </x:font>
+    <x:font>
+      <x:sz val="11"/>
+      <x:name val="等线"/>
+    </x:font>
+    <x:font>
+      <x:b/>
+      <x:sz val="11"/>
+      <x:color rgb="FFFFFFFF"/>
+      <x:name val="等线"/>
+    </x:font>
   </x:fonts>
-  <x:fills count="7">
+  <x:fills count="14">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -93,6 +120,41 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor rgb="FF64748B"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFEDF2F7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF6F8FA"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FF1F4E78"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFD9EAF7"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFF5F7FA"/>
       </x:patternFill>
     </x:fill>
   </x:fills>
@@ -180,7 +242,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="38">
+  <x:cellXfs count="55">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -290,6 +352,57 @@
     </x:xf>
     <x:xf numFmtId="200" fontId="1" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="9" fillId="7" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="10" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="9" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="8" fillId="10" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="12" fillId="11" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="12" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="11" fillId="13" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center" wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
@@ -497,6 +610,14 @@
     <x:col min="2" max="2" width="16" hidden="0" customWidth="1"/>
     <x:col min="3" max="3" width="24" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="20" hidden="0" customWidth="1"/>
+    <x:col min="5" max="5" width="24" hidden="0" customWidth="1"/>
+    <x:col min="6" max="6" width="24" hidden="0" customWidth="1"/>
+    <x:col min="7" max="7" width="24" hidden="0" customWidth="1"/>
+    <x:col min="8" max="8" width="29" hidden="0" customWidth="1"/>
+    <x:col min="9" max="9" width="29" hidden="0" customWidth="1"/>
+    <x:col min="10" max="10" width="29" hidden="0" customWidth="1"/>
+    <x:col min="11" max="11" width="29" hidden="0" customWidth="1"/>
+    <x:col min="12" max="12" width="29" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="30" customHeight="1">
@@ -512,6 +633,30 @@
       <x:c r="D1" s="11" t="str">
         <x:v>visualSetId</x:v>
       </x:c>
+      <x:c r="E1" s="43" t="str">
+        <x:v>attributeProfileId</x:v>
+      </x:c>
+      <x:c r="F1" s="43" t="str">
+        <x:v>defaultSkillId</x:v>
+      </x:c>
+      <x:c r="G1" s="43" t="str">
+        <x:v>bodyRadius</x:v>
+      </x:c>
+      <x:c r="H1" s="52" t="str">
+        <x:v>moveRadiusPixels</x:v>
+      </x:c>
+      <x:c r="I1" s="52" t="str">
+        <x:v>moveHeightPixels</x:v>
+      </x:c>
+      <x:c r="J1" s="52" t="str">
+        <x:v>moveOffsetXPixels</x:v>
+      </x:c>
+      <x:c r="K1" s="52" t="str">
+        <x:v>moveOffsetYPixels</x:v>
+      </x:c>
+      <x:c r="L1" s="52" t="str">
+        <x:v>moveElevationPixels</x:v>
+      </x:c>
     </x:row>
     <x:row r="2" ht="30" customHeight="1">
       <x:c r="A2" s="29" t="str">
@@ -526,6 +671,30 @@
       <x:c r="D2" s="14" t="str">
         <x:v>int#ref=TbVisualSet</x:v>
       </x:c>
+      <x:c r="E2" s="45" t="str">
+        <x:v>int?#ref=TbAttributeProfile</x:v>
+      </x:c>
+      <x:c r="F2" s="45" t="str">
+        <x:v>int?#ref=TbSkill</x:v>
+      </x:c>
+      <x:c r="G2" s="45" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="H2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="I2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="J2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="K2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="L2" s="53" t="str">
+        <x:v>float?</x:v>
+      </x:c>
     </x:row>
     <x:row r="3" ht="30" customHeight="1">
       <x:c r="A3" s="30" t="str">
@@ -534,8 +703,16 @@
       <x:c r="B3" s="16"/>
       <x:c r="C3" s="16"/>
       <x:c r="D3" s="16"/>
-    </x:row>
-    <x:row r="4" ht="30" customHeight="1">
+      <x:c r="E3" s="46"/>
+      <x:c r="F3" s="46"/>
+      <x:c r="G3" s="46"/>
+      <x:c r="H3" s="50"/>
+      <x:c r="I3" s="50"/>
+      <x:c r="J3" s="50"/>
+      <x:c r="K3" s="50"/>
+      <x:c r="L3" s="50"/>
+    </x:row>
+    <x:row r="4" ht="70" customHeight="1">
       <x:c r="A4" s="31" t="str">
         <x:v>##</x:v>
       </x:c>
@@ -547,6 +724,30 @@
       </x:c>
       <x:c r="D4" s="24" t="str">
         <x:v>怪物表现集合ID</x:v>
+      </x:c>
+      <x:c r="E4" s="47" t="str">
+        <x:v>战斗属性方案；空值仅可预览</x:v>
+      </x:c>
+      <x:c r="F4" s="47" t="str">
+        <x:v>默认装备技能；不同于已解锁技能</x:v>
+      </x:c>
+      <x:c r="G4" s="47" t="str">
+        <x:v>伤害判定身体半径，世界单位；独立于移动圆柱</x:v>
+      </x:c>
+      <x:c r="H4" s="54" t="str">
+        <x:v>移动圆柱半径，逻辑像素；由预制体导出</x:v>
+      </x:c>
+      <x:c r="I4" s="54" t="str">
+        <x:v>移动圆柱高度，逻辑像素；由预制体导出</x:v>
+      </x:c>
+      <x:c r="J4" s="54" t="str">
+        <x:v>圆柱底心横向偏移，逻辑像素</x:v>
+      </x:c>
+      <x:c r="K4" s="54" t="str">
+        <x:v>圆柱底心地面纵向偏移，逻辑像素</x:v>
+      </x:c>
+      <x:c r="L4" s="54" t="str">
+        <x:v>圆柱底面离地高度，逻辑像素</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -560,6 +761,30 @@
       <x:c r="D5" s="35" t="n">
         <x:v>20001</x:v>
       </x:c>
+      <x:c r="E5" s="41" t="n">
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F5" s="41" t="n">
+        <x:v>20002</x:v>
+      </x:c>
+      <x:c r="G5" s="41" t="n">
+        <x:v>0.2</x:v>
+      </x:c>
+      <x:c r="H5" s="50">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I5" s="50">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="J5" s="50">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="50">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L5" s="50">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="6">
       <x:c r="A6" s="33"/>
@@ -572,6 +797,24 @@
       <x:c r="D6" s="36" t="n">
         <x:v>20002</x:v>
       </x:c>
+      <x:c r="E6" s="41"/>
+      <x:c r="F6" s="41"/>
+      <x:c r="G6" s="41"/>
+      <x:c r="H6">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I6">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="J6">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L6">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="7">
       <x:c r="A7" s="33"/>
@@ -584,6 +827,24 @@
       <x:c r="D7" s="36" t="n">
         <x:v>20003</x:v>
       </x:c>
+      <x:c r="E7" s="41"/>
+      <x:c r="F7" s="41"/>
+      <x:c r="G7" s="41"/>
+      <x:c r="H7">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I7">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="J7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L7">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="8">
       <x:c r="A8" s="33"/>
@@ -596,6 +857,24 @@
       <x:c r="D8" s="36" t="n">
         <x:v>20004</x:v>
       </x:c>
+      <x:c r="E8" s="41"/>
+      <x:c r="F8" s="41"/>
+      <x:c r="G8" s="41"/>
+      <x:c r="H8">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I8">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="J8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L8">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="9">
       <x:c r="A9" s="33"/>
@@ -608,6 +887,24 @@
       <x:c r="D9" s="36" t="n">
         <x:v>20005</x:v>
       </x:c>
+      <x:c r="E9" s="41"/>
+      <x:c r="F9" s="41"/>
+      <x:c r="G9" s="41"/>
+      <x:c r="H9">
+        <x:v>61.0000038</x:v>
+      </x:c>
+      <x:c r="I9">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="J9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K9">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L9">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="10">
       <x:c r="A10" s="33"/>
@@ -620,6 +917,24 @@
       <x:c r="D10" s="36" t="n">
         <x:v>20006</x:v>
       </x:c>
+      <x:c r="E10" s="41"/>
+      <x:c r="F10" s="41"/>
+      <x:c r="G10" s="41"/>
+      <x:c r="H10">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I10">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="J10">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L10">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="11">
       <x:c r="A11" s="33"/>
@@ -632,6 +947,24 @@
       <x:c r="D11" s="36" t="n">
         <x:v>20007</x:v>
       </x:c>
+      <x:c r="E11" s="41"/>
+      <x:c r="F11" s="41"/>
+      <x:c r="G11" s="41"/>
+      <x:c r="H11">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I11">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L11">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="12">
       <x:c r="A12" s="33"/>
@@ -644,6 +977,24 @@
       <x:c r="D12" s="36" t="n">
         <x:v>20008</x:v>
       </x:c>
+      <x:c r="E12" s="41"/>
+      <x:c r="F12" s="41"/>
+      <x:c r="G12" s="41"/>
+      <x:c r="H12">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I12">
+        <x:v>175.999985</x:v>
+      </x:c>
+      <x:c r="J12">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L12">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="13">
       <x:c r="A13" s="33"/>
@@ -656,6 +1007,24 @@
       <x:c r="D13" s="36" t="n">
         <x:v>20009</x:v>
       </x:c>
+      <x:c r="E13" s="41"/>
+      <x:c r="F13" s="41"/>
+      <x:c r="G13" s="41"/>
+      <x:c r="H13">
+        <x:v>60.4999962</x:v>
+      </x:c>
+      <x:c r="I13">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L13">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="14">
       <x:c r="A14" s="33"/>
@@ -668,6 +1037,24 @@
       <x:c r="D14" s="36" t="n">
         <x:v>20010</x:v>
       </x:c>
+      <x:c r="E14" s="41"/>
+      <x:c r="F14" s="41"/>
+      <x:c r="G14" s="41"/>
+      <x:c r="H14">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I14">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="J14">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L14">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="15">
       <x:c r="A15" s="33"/>
@@ -680,6 +1067,24 @@
       <x:c r="D15" s="36" t="n">
         <x:v>20011</x:v>
       </x:c>
+      <x:c r="E15" s="41"/>
+      <x:c r="F15" s="41"/>
+      <x:c r="G15" s="41"/>
+      <x:c r="H15">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I15">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J15">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L15">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="16">
       <x:c r="A16" s="33"/>
@@ -692,6 +1097,24 @@
       <x:c r="D16" s="36" t="n">
         <x:v>20012</x:v>
       </x:c>
+      <x:c r="E16" s="41"/>
+      <x:c r="F16" s="41"/>
+      <x:c r="G16" s="41"/>
+      <x:c r="H16">
+        <x:v>27.9999981</x:v>
+      </x:c>
+      <x:c r="I16">
+        <x:v>110.999992</x:v>
+      </x:c>
+      <x:c r="J16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L16">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="17">
       <x:c r="A17" s="33"/>
@@ -704,6 +1127,24 @@
       <x:c r="D17" s="36" t="n">
         <x:v>20013</x:v>
       </x:c>
+      <x:c r="E17" s="41"/>
+      <x:c r="F17" s="41"/>
+      <x:c r="G17" s="41"/>
+      <x:c r="H17">
+        <x:v>43.5</x:v>
+      </x:c>
+      <x:c r="I17">
+        <x:v>120.000008</x:v>
+      </x:c>
+      <x:c r="J17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L17">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="18">
       <x:c r="A18" s="33"/>
@@ -716,6 +1157,24 @@
       <x:c r="D18" s="36" t="n">
         <x:v>20014</x:v>
       </x:c>
+      <x:c r="E18" s="41"/>
+      <x:c r="F18" s="41"/>
+      <x:c r="G18" s="41"/>
+      <x:c r="H18">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="I18">
+        <x:v>212.999985</x:v>
+      </x:c>
+      <x:c r="J18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L18">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="19">
       <x:c r="A19" s="33"/>
@@ -728,6 +1187,24 @@
       <x:c r="D19" s="36" t="n">
         <x:v>20015</x:v>
       </x:c>
+      <x:c r="E19" s="41"/>
+      <x:c r="F19" s="41"/>
+      <x:c r="G19" s="41"/>
+      <x:c r="H19">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I19">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="J19">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L19">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="20">
       <x:c r="A20" s="33"/>
@@ -740,6 +1217,24 @@
       <x:c r="D20" s="36" t="n">
         <x:v>20016</x:v>
       </x:c>
+      <x:c r="E20" s="41"/>
+      <x:c r="F20" s="41"/>
+      <x:c r="G20" s="41"/>
+      <x:c r="H20">
+        <x:v>55.9999962</x:v>
+      </x:c>
+      <x:c r="I20">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J20">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L20">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="21">
       <x:c r="A21" s="33"/>
@@ -752,6 +1247,24 @@
       <x:c r="D21" s="36" t="n">
         <x:v>20017</x:v>
       </x:c>
+      <x:c r="E21" s="41"/>
+      <x:c r="F21" s="41"/>
+      <x:c r="G21" s="41"/>
+      <x:c r="H21">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I21">
+        <x:v>170.000015</x:v>
+      </x:c>
+      <x:c r="J21">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K21">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L21">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="22">
       <x:c r="A22" s="33"/>
@@ -764,6 +1277,24 @@
       <x:c r="D22" s="36" t="n">
         <x:v>20018</x:v>
       </x:c>
+      <x:c r="E22" s="41"/>
+      <x:c r="F22" s="41"/>
+      <x:c r="G22" s="41"/>
+      <x:c r="H22">
+        <x:v>47.5</x:v>
+      </x:c>
+      <x:c r="I22">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="J22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L22">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="23">
       <x:c r="A23" s="33"/>
@@ -776,6 +1307,24 @@
       <x:c r="D23" s="36" t="n">
         <x:v>20019</x:v>
       </x:c>
+      <x:c r="E23" s="41"/>
+      <x:c r="F23" s="41"/>
+      <x:c r="G23" s="41"/>
+      <x:c r="H23">
+        <x:v>83.5</x:v>
+      </x:c>
+      <x:c r="I23">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="J23">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K23">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L23">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="24">
       <x:c r="A24" s="33"/>
@@ -788,6 +1337,24 @@
       <x:c r="D24" s="36" t="n">
         <x:v>20020</x:v>
       </x:c>
+      <x:c r="E24" s="41"/>
+      <x:c r="F24" s="41"/>
+      <x:c r="G24" s="41"/>
+      <x:c r="H24">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I24">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J24">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K24">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L24">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="25">
       <x:c r="A25" s="33"/>
@@ -800,6 +1367,24 @@
       <x:c r="D25" s="36" t="n">
         <x:v>20021</x:v>
       </x:c>
+      <x:c r="E25" s="41"/>
+      <x:c r="F25" s="41"/>
+      <x:c r="G25" s="41"/>
+      <x:c r="H25">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I25">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="J25">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K25">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L25">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="26">
       <x:c r="A26" s="33"/>
@@ -812,6 +1397,24 @@
       <x:c r="D26" s="36" t="n">
         <x:v>20022</x:v>
       </x:c>
+      <x:c r="E26" s="41"/>
+      <x:c r="F26" s="41"/>
+      <x:c r="G26" s="41"/>
+      <x:c r="H26">
+        <x:v>95.99999</x:v>
+      </x:c>
+      <x:c r="I26">
+        <x:v>187.999985</x:v>
+      </x:c>
+      <x:c r="J26">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K26">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L26">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="27">
       <x:c r="A27" s="33"/>
@@ -824,6 +1427,24 @@
       <x:c r="D27" s="36" t="n">
         <x:v>20023</x:v>
       </x:c>
+      <x:c r="E27" s="41"/>
+      <x:c r="F27" s="41"/>
+      <x:c r="G27" s="41"/>
+      <x:c r="H27">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="I27">
+        <x:v>252</x:v>
+      </x:c>
+      <x:c r="J27">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K27">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L27">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="28">
       <x:c r="A28" s="33"/>
@@ -836,6 +1457,24 @@
       <x:c r="D28" s="36" t="n">
         <x:v>20024</x:v>
       </x:c>
+      <x:c r="E28" s="41"/>
+      <x:c r="F28" s="41"/>
+      <x:c r="G28" s="41"/>
+      <x:c r="H28">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I28">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="J28">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L28">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="29">
       <x:c r="A29" s="33"/>
@@ -848,6 +1487,24 @@
       <x:c r="D29" s="36" t="n">
         <x:v>20025</x:v>
       </x:c>
+      <x:c r="E29" s="41"/>
+      <x:c r="F29" s="41"/>
+      <x:c r="G29" s="41"/>
+      <x:c r="H29">
+        <x:v>85.50001</x:v>
+      </x:c>
+      <x:c r="I29">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="J29">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L29">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="30">
       <x:c r="A30" s="33"/>
@@ -860,6 +1517,24 @@
       <x:c r="D30" s="36" t="n">
         <x:v>20026</x:v>
       </x:c>
+      <x:c r="E30" s="41"/>
+      <x:c r="F30" s="41"/>
+      <x:c r="G30" s="41"/>
+      <x:c r="H30">
+        <x:v>54.5000038</x:v>
+      </x:c>
+      <x:c r="I30">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J30">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L30">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="31">
       <x:c r="A31" s="33"/>
@@ -872,6 +1547,24 @@
       <x:c r="D31" s="36" t="n">
         <x:v>20027</x:v>
       </x:c>
+      <x:c r="E31" s="41"/>
+      <x:c r="F31" s="41"/>
+      <x:c r="G31" s="41"/>
+      <x:c r="H31">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I31">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J31">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L31">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="32">
       <x:c r="A32" s="33"/>
@@ -884,6 +1577,24 @@
       <x:c r="D32" s="36" t="n">
         <x:v>20028</x:v>
       </x:c>
+      <x:c r="E32" s="41"/>
+      <x:c r="F32" s="41"/>
+      <x:c r="G32" s="41"/>
+      <x:c r="H32">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I32">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J32">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K32">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L32">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="33">
       <x:c r="A33" s="33"/>
@@ -896,6 +1607,24 @@
       <x:c r="D33" s="36" t="n">
         <x:v>20029</x:v>
       </x:c>
+      <x:c r="E33" s="41"/>
+      <x:c r="F33" s="41"/>
+      <x:c r="G33" s="41"/>
+      <x:c r="H33">
+        <x:v>43.5</x:v>
+      </x:c>
+      <x:c r="I33">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="J33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K33">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L33">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="34">
       <x:c r="A34" s="33"/>
@@ -908,6 +1637,24 @@
       <x:c r="D34" s="36" t="n">
         <x:v>20030</x:v>
       </x:c>
+      <x:c r="E34" s="41"/>
+      <x:c r="F34" s="41"/>
+      <x:c r="G34" s="41"/>
+      <x:c r="H34">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I34">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="J34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K34">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L34">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="35">
       <x:c r="A35" s="33"/>
@@ -920,6 +1667,24 @@
       <x:c r="D35" s="36" t="n">
         <x:v>20031</x:v>
       </x:c>
+      <x:c r="E35" s="41"/>
+      <x:c r="F35" s="41"/>
+      <x:c r="G35" s="41"/>
+      <x:c r="H35">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I35">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J35">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K35">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L35">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="36">
       <x:c r="A36" s="33"/>
@@ -932,6 +1697,24 @@
       <x:c r="D36" s="36" t="n">
         <x:v>20032</x:v>
       </x:c>
+      <x:c r="E36" s="41"/>
+      <x:c r="F36" s="41"/>
+      <x:c r="G36" s="41"/>
+      <x:c r="H36">
+        <x:v>84.00001</x:v>
+      </x:c>
+      <x:c r="I36">
+        <x:v>253</x:v>
+      </x:c>
+      <x:c r="J36">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K36">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L36">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="37">
       <x:c r="A37" s="33"/>
@@ -944,6 +1727,24 @@
       <x:c r="D37" s="36" t="n">
         <x:v>20033</x:v>
       </x:c>
+      <x:c r="E37" s="41"/>
+      <x:c r="F37" s="41"/>
+      <x:c r="G37" s="41"/>
+      <x:c r="H37">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I37">
+        <x:v>215.999985</x:v>
+      </x:c>
+      <x:c r="J37">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K37">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L37">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="38">
       <x:c r="A38" s="33"/>
@@ -956,6 +1757,24 @@
       <x:c r="D38" s="36" t="n">
         <x:v>20034</x:v>
       </x:c>
+      <x:c r="E38" s="41"/>
+      <x:c r="F38" s="41"/>
+      <x:c r="G38" s="41"/>
+      <x:c r="H38">
+        <x:v>62.5</x:v>
+      </x:c>
+      <x:c r="I38">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J38">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K38">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L38">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="39">
       <x:c r="A39" s="33"/>
@@ -968,6 +1787,24 @@
       <x:c r="D39" s="36" t="n">
         <x:v>20035</x:v>
       </x:c>
+      <x:c r="E39" s="41"/>
+      <x:c r="F39" s="41"/>
+      <x:c r="G39" s="41"/>
+      <x:c r="H39">
+        <x:v>69.5</x:v>
+      </x:c>
+      <x:c r="I39">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J39">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K39">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L39">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="40">
       <x:c r="A40" s="33"/>
@@ -980,6 +1817,24 @@
       <x:c r="D40" s="36" t="n">
         <x:v>20036</x:v>
       </x:c>
+      <x:c r="E40" s="41"/>
+      <x:c r="F40" s="41"/>
+      <x:c r="G40" s="41"/>
+      <x:c r="H40">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I40">
+        <x:v>197</x:v>
+      </x:c>
+      <x:c r="J40">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L40">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="41">
       <x:c r="A41" s="33"/>
@@ -992,6 +1847,24 @@
       <x:c r="D41" s="36" t="n">
         <x:v>20037</x:v>
       </x:c>
+      <x:c r="E41" s="41"/>
+      <x:c r="F41" s="41"/>
+      <x:c r="G41" s="41"/>
+      <x:c r="H41">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="I41">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="J41">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K41">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L41">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="42">
       <x:c r="A42" s="33"/>
@@ -1004,6 +1877,24 @@
       <x:c r="D42" s="36" t="n">
         <x:v>20038</x:v>
       </x:c>
+      <x:c r="E42" s="41"/>
+      <x:c r="F42" s="41"/>
+      <x:c r="G42" s="41"/>
+      <x:c r="H42">
+        <x:v>62.5</x:v>
+      </x:c>
+      <x:c r="I42">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="J42">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K42">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L42">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="43">
       <x:c r="A43" s="33"/>
@@ -1016,6 +1907,24 @@
       <x:c r="D43" s="36" t="n">
         <x:v>20039</x:v>
       </x:c>
+      <x:c r="E43" s="41"/>
+      <x:c r="F43" s="41"/>
+      <x:c r="G43" s="41"/>
+      <x:c r="H43">
+        <x:v>69.5</x:v>
+      </x:c>
+      <x:c r="I43">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J43">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K43">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L43">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="44">
       <x:c r="A44" s="33"/>
@@ -1028,6 +1937,24 @@
       <x:c r="D44" s="36" t="n">
         <x:v>20040</x:v>
       </x:c>
+      <x:c r="E44" s="41"/>
+      <x:c r="F44" s="41"/>
+      <x:c r="G44" s="41"/>
+      <x:c r="H44">
+        <x:v>64.5</x:v>
+      </x:c>
+      <x:c r="I44">
+        <x:v>254</x:v>
+      </x:c>
+      <x:c r="J44">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K44">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L44">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="45">
       <x:c r="A45" s="33"/>
@@ -1040,6 +1967,24 @@
       <x:c r="D45" s="36" t="n">
         <x:v>20041</x:v>
       </x:c>
+      <x:c r="E45" s="41"/>
+      <x:c r="F45" s="41"/>
+      <x:c r="G45" s="41"/>
+      <x:c r="H45">
+        <x:v>55.4999962</x:v>
+      </x:c>
+      <x:c r="I45">
+        <x:v>217.999985</x:v>
+      </x:c>
+      <x:c r="J45">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K45">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L45">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="46">
       <x:c r="A46" s="33"/>
@@ -1052,6 +1997,24 @@
       <x:c r="D46" s="36" t="n">
         <x:v>20042</x:v>
       </x:c>
+      <x:c r="E46" s="41"/>
+      <x:c r="F46" s="41"/>
+      <x:c r="G46" s="41"/>
+      <x:c r="H46">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I46">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="J46">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K46">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L46">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="47">
       <x:c r="A47" s="33"/>
@@ -1064,6 +2027,24 @@
       <x:c r="D47" s="36" t="n">
         <x:v>20043</x:v>
       </x:c>
+      <x:c r="E47" s="41"/>
+      <x:c r="F47" s="41"/>
+      <x:c r="G47" s="41"/>
+      <x:c r="H47">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I47">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="J47">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K47">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L47">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="48">
       <x:c r="A48" s="33"/>
@@ -1076,6 +2057,24 @@
       <x:c r="D48" s="36" t="n">
         <x:v>20044</x:v>
       </x:c>
+      <x:c r="E48" s="41"/>
+      <x:c r="F48" s="41"/>
+      <x:c r="G48" s="41"/>
+      <x:c r="H48">
+        <x:v>55.0000038</x:v>
+      </x:c>
+      <x:c r="I48">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="J48">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K48">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L48">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="49">
       <x:c r="A49" s="33"/>
@@ -1088,6 +2087,24 @@
       <x:c r="D49" s="36" t="n">
         <x:v>20045</x:v>
       </x:c>
+      <x:c r="E49" s="41"/>
+      <x:c r="F49" s="41"/>
+      <x:c r="G49" s="41"/>
+      <x:c r="H49">
+        <x:v>50.5</x:v>
+      </x:c>
+      <x:c r="I49">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="J49">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K49">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L49">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="50">
       <x:c r="A50" s="33"/>
@@ -1100,6 +2117,24 @@
       <x:c r="D50" s="36" t="n">
         <x:v>20046</x:v>
       </x:c>
+      <x:c r="E50" s="41"/>
+      <x:c r="F50" s="41"/>
+      <x:c r="G50" s="41"/>
+      <x:c r="H50">
+        <x:v>119.999992</x:v>
+      </x:c>
+      <x:c r="I50">
+        <x:v>260</x:v>
+      </x:c>
+      <x:c r="J50">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K50">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L50">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="51">
       <x:c r="A51" s="33"/>
@@ -1112,6 +2147,24 @@
       <x:c r="D51" s="36" t="n">
         <x:v>20047</x:v>
       </x:c>
+      <x:c r="E51" s="41"/>
+      <x:c r="F51" s="41"/>
+      <x:c r="G51" s="41"/>
+      <x:c r="H51">
+        <x:v>65.5</x:v>
+      </x:c>
+      <x:c r="I51">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J51">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K51">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L51">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="52">
       <x:c r="A52" s="33"/>
@@ -1124,6 +2177,24 @@
       <x:c r="D52" s="36" t="n">
         <x:v>20048</x:v>
       </x:c>
+      <x:c r="E52" s="41"/>
+      <x:c r="F52" s="41"/>
+      <x:c r="G52" s="41"/>
+      <x:c r="H52">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="I52">
+        <x:v>218.000015</x:v>
+      </x:c>
+      <x:c r="J52">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K52">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L52">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="53">
       <x:c r="A53" s="33"/>
@@ -1136,6 +2207,24 @@
       <x:c r="D53" s="36" t="n">
         <x:v>20049</x:v>
       </x:c>
+      <x:c r="E53" s="41"/>
+      <x:c r="F53" s="41"/>
+      <x:c r="G53" s="41"/>
+      <x:c r="H53">
+        <x:v>109.000008</x:v>
+      </x:c>
+      <x:c r="I53">
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="J53">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K53">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L53">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="54">
       <x:c r="A54" s="33"/>
@@ -1148,6 +2237,24 @@
       <x:c r="D54" s="36" t="n">
         <x:v>20050</x:v>
       </x:c>
+      <x:c r="E54" s="41"/>
+      <x:c r="F54" s="41"/>
+      <x:c r="G54" s="41"/>
+      <x:c r="H54">
+        <x:v>59.9999962</x:v>
+      </x:c>
+      <x:c r="I54">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K54">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L54">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="55">
       <x:c r="A55" s="33"/>
@@ -1160,6 +2267,24 @@
       <x:c r="D55" s="36" t="n">
         <x:v>20051</x:v>
       </x:c>
+      <x:c r="E55" s="41"/>
+      <x:c r="F55" s="41"/>
+      <x:c r="G55" s="41"/>
+      <x:c r="H55">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I55">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="J55">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K55">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L55">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="56">
       <x:c r="A56" s="33"/>
@@ -1172,6 +2297,24 @@
       <x:c r="D56" s="36" t="n">
         <x:v>20052</x:v>
       </x:c>
+      <x:c r="E56" s="41"/>
+      <x:c r="F56" s="41"/>
+      <x:c r="G56" s="41"/>
+      <x:c r="H56">
+        <x:v>49.0000038</x:v>
+      </x:c>
+      <x:c r="I56">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="J56">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K56">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L56">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="57">
       <x:c r="A57" s="33"/>
@@ -1184,6 +2327,24 @@
       <x:c r="D57" s="36" t="n">
         <x:v>20053</x:v>
       </x:c>
+      <x:c r="E57" s="41"/>
+      <x:c r="F57" s="41"/>
+      <x:c r="G57" s="41"/>
+      <x:c r="H57">
+        <x:v>132.500015</x:v>
+      </x:c>
+      <x:c r="I57">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="J57">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K57">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L57">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="58">
       <x:c r="A58" s="33"/>
@@ -1196,6 +2357,24 @@
       <x:c r="D58" s="36" t="n">
         <x:v>20054</x:v>
       </x:c>
+      <x:c r="E58" s="41"/>
+      <x:c r="F58" s="41"/>
+      <x:c r="G58" s="41"/>
+      <x:c r="H58">
+        <x:v>46.9999962</x:v>
+      </x:c>
+      <x:c r="I58">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="J58">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K58">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L58">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="59">
       <x:c r="A59" s="33"/>
@@ -1208,6 +2387,24 @@
       <x:c r="D59" s="36" t="n">
         <x:v>20055</x:v>
       </x:c>
+      <x:c r="E59" s="41"/>
+      <x:c r="F59" s="41"/>
+      <x:c r="G59" s="41"/>
+      <x:c r="H59">
+        <x:v>38.5</x:v>
+      </x:c>
+      <x:c r="I59">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J59">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K59">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L59">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="60">
       <x:c r="A60" s="33"/>
@@ -1220,6 +2417,24 @@
       <x:c r="D60" s="36" t="n">
         <x:v>20056</x:v>
       </x:c>
+      <x:c r="E60" s="41"/>
+      <x:c r="F60" s="41"/>
+      <x:c r="G60" s="41"/>
+      <x:c r="H60">
+        <x:v>54.4999962</x:v>
+      </x:c>
+      <x:c r="I60">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J60">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K60">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L60">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="61">
       <x:c r="A61" s="33"/>
@@ -1232,6 +2447,24 @@
       <x:c r="D61" s="36" t="n">
         <x:v>20057</x:v>
       </x:c>
+      <x:c r="E61" s="41"/>
+      <x:c r="F61" s="41"/>
+      <x:c r="G61" s="41"/>
+      <x:c r="H61">
+        <x:v>55.4999962</x:v>
+      </x:c>
+      <x:c r="I61">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J61">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K61">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L61">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="62">
       <x:c r="A62" s="33"/>
@@ -1244,6 +2477,24 @@
       <x:c r="D62" s="36" t="n">
         <x:v>20058</x:v>
       </x:c>
+      <x:c r="E62" s="41"/>
+      <x:c r="F62" s="41"/>
+      <x:c r="G62" s="41"/>
+      <x:c r="H62">
+        <x:v>43.5</x:v>
+      </x:c>
+      <x:c r="I62">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="J62">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K62">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L62">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="63">
       <x:c r="A63" s="33"/>
@@ -1256,6 +2507,24 @@
       <x:c r="D63" s="36" t="n">
         <x:v>20059</x:v>
       </x:c>
+      <x:c r="E63" s="41"/>
+      <x:c r="F63" s="41"/>
+      <x:c r="G63" s="41"/>
+      <x:c r="H63">
+        <x:v>56.5</x:v>
+      </x:c>
+      <x:c r="I63">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="J63">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K63">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L63">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="64">
       <x:c r="A64" s="33"/>
@@ -1268,6 +2537,24 @@
       <x:c r="D64" s="36" t="n">
         <x:v>20060</x:v>
       </x:c>
+      <x:c r="E64" s="41"/>
+      <x:c r="F64" s="41"/>
+      <x:c r="G64" s="41"/>
+      <x:c r="H64">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="I64">
+        <x:v>214.999985</x:v>
+      </x:c>
+      <x:c r="J64">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K64">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L64">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="65">
       <x:c r="A65" s="33"/>
@@ -1280,6 +2567,24 @@
       <x:c r="D65" s="36" t="n">
         <x:v>20061</x:v>
       </x:c>
+      <x:c r="E65" s="41"/>
+      <x:c r="F65" s="41"/>
+      <x:c r="G65" s="41"/>
+      <x:c r="H65">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I65">
+        <x:v>187.999985</x:v>
+      </x:c>
+      <x:c r="J65">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K65">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L65">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="66">
       <x:c r="A66" s="33"/>
@@ -1292,6 +2597,24 @@
       <x:c r="D66" s="36" t="n">
         <x:v>20062</x:v>
       </x:c>
+      <x:c r="E66" s="41"/>
+      <x:c r="F66" s="41"/>
+      <x:c r="G66" s="41"/>
+      <x:c r="H66">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I66">
+        <x:v>215.999985</x:v>
+      </x:c>
+      <x:c r="J66">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K66">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L66">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="67">
       <x:c r="A67" s="33"/>
@@ -1304,6 +2627,24 @@
       <x:c r="D67" s="36" t="n">
         <x:v>20063</x:v>
       </x:c>
+      <x:c r="E67" s="41"/>
+      <x:c r="F67" s="41"/>
+      <x:c r="G67" s="41"/>
+      <x:c r="H67">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I67">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="J67">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K67">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L67">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="68">
       <x:c r="A68" s="33"/>
@@ -1316,6 +2657,24 @@
       <x:c r="D68" s="36" t="n">
         <x:v>20064</x:v>
       </x:c>
+      <x:c r="E68" s="41"/>
+      <x:c r="F68" s="41"/>
+      <x:c r="G68" s="41"/>
+      <x:c r="H68">
+        <x:v>52.5</x:v>
+      </x:c>
+      <x:c r="I68">
+        <x:v>174.999985</x:v>
+      </x:c>
+      <x:c r="J68">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K68">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L68">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="69">
       <x:c r="A69" s="33"/>
@@ -1328,6 +2687,24 @@
       <x:c r="D69" s="36" t="n">
         <x:v>20065</x:v>
       </x:c>
+      <x:c r="E69" s="41"/>
+      <x:c r="F69" s="41"/>
+      <x:c r="G69" s="41"/>
+      <x:c r="H69">
+        <x:v>77.5</x:v>
+      </x:c>
+      <x:c r="I69">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="J69">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K69">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L69">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="70">
       <x:c r="A70" s="33"/>
@@ -1340,6 +2717,24 @@
       <x:c r="D70" s="36" t="n">
         <x:v>20066</x:v>
       </x:c>
+      <x:c r="E70" s="41"/>
+      <x:c r="F70" s="41"/>
+      <x:c r="G70" s="41"/>
+      <x:c r="H70">
+        <x:v>56.5</x:v>
+      </x:c>
+      <x:c r="I70">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J70">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K70">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L70">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="71">
       <x:c r="A71" s="33"/>
@@ -1352,6 +2747,24 @@
       <x:c r="D71" s="36" t="n">
         <x:v>20067</x:v>
       </x:c>
+      <x:c r="E71" s="41"/>
+      <x:c r="F71" s="41"/>
+      <x:c r="G71" s="41"/>
+      <x:c r="H71">
+        <x:v>60.5000038</x:v>
+      </x:c>
+      <x:c r="I71">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="J71">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K71">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L71">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="72">
       <x:c r="A72" s="33"/>
@@ -1364,6 +2777,24 @@
       <x:c r="D72" s="36" t="n">
         <x:v>20068</x:v>
       </x:c>
+      <x:c r="E72" s="41"/>
+      <x:c r="F72" s="41"/>
+      <x:c r="G72" s="41"/>
+      <x:c r="H72">
+        <x:v>68.5</x:v>
+      </x:c>
+      <x:c r="I72">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="J72">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K72">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L72">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="73">
       <x:c r="A73" s="33"/>
@@ -1376,6 +2807,24 @@
       <x:c r="D73" s="36" t="n">
         <x:v>20069</x:v>
       </x:c>
+      <x:c r="E73" s="41"/>
+      <x:c r="F73" s="41"/>
+      <x:c r="G73" s="41"/>
+      <x:c r="H73">
+        <x:v>59.5000038</x:v>
+      </x:c>
+      <x:c r="I73">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="J73">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K73">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L73">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="74">
       <x:c r="A74" s="33"/>
@@ -1388,6 +2837,24 @@
       <x:c r="D74" s="36" t="n">
         <x:v>20070</x:v>
       </x:c>
+      <x:c r="E74" s="41"/>
+      <x:c r="F74" s="41"/>
+      <x:c r="G74" s="41"/>
+      <x:c r="H74">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I74">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="J74">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K74">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L74">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="75">
       <x:c r="A75" s="33"/>
@@ -1400,6 +2867,24 @@
       <x:c r="D75" s="36" t="n">
         <x:v>20071</x:v>
       </x:c>
+      <x:c r="E75" s="41"/>
+      <x:c r="F75" s="41"/>
+      <x:c r="G75" s="41"/>
+      <x:c r="H75">
+        <x:v>35.5000038</x:v>
+      </x:c>
+      <x:c r="I75">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J75">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K75">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L75">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="76">
       <x:c r="A76" s="33"/>
@@ -1412,6 +2897,24 @@
       <x:c r="D76" s="36" t="n">
         <x:v>20072</x:v>
       </x:c>
+      <x:c r="E76" s="41"/>
+      <x:c r="F76" s="41"/>
+      <x:c r="G76" s="41"/>
+      <x:c r="H76">
+        <x:v>38.5</x:v>
+      </x:c>
+      <x:c r="I76">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="J76">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K76">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L76">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="77">
       <x:c r="A77" s="33"/>
@@ -1424,6 +2927,24 @@
       <x:c r="D77" s="36" t="n">
         <x:v>20073</x:v>
       </x:c>
+      <x:c r="E77" s="41"/>
+      <x:c r="F77" s="41"/>
+      <x:c r="G77" s="41"/>
+      <x:c r="H77">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="I77">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="J77">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K77">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L77">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="78">
       <x:c r="A78" s="33"/>
@@ -1436,6 +2957,24 @@
       <x:c r="D78" s="36" t="n">
         <x:v>20074</x:v>
       </x:c>
+      <x:c r="E78" s="41"/>
+      <x:c r="F78" s="41"/>
+      <x:c r="G78" s="41"/>
+      <x:c r="H78">
+        <x:v>93.5</x:v>
+      </x:c>
+      <x:c r="I78">
+        <x:v>218.999985</x:v>
+      </x:c>
+      <x:c r="J78">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K78">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L78">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="79">
       <x:c r="A79" s="33"/>
@@ -1448,6 +2987,24 @@
       <x:c r="D79" s="36" t="n">
         <x:v>20075</x:v>
       </x:c>
+      <x:c r="E79" s="41"/>
+      <x:c r="F79" s="41"/>
+      <x:c r="G79" s="41"/>
+      <x:c r="H79">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I79">
+        <x:v>121.999992</x:v>
+      </x:c>
+      <x:c r="J79">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K79">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L79">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="80">
       <x:c r="A80" s="33"/>
@@ -1460,6 +3017,24 @@
       <x:c r="D80" s="36" t="n">
         <x:v>20076</x:v>
       </x:c>
+      <x:c r="E80" s="41"/>
+      <x:c r="F80" s="41"/>
+      <x:c r="G80" s="41"/>
+      <x:c r="H80">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I80">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J80">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K80">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L80">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="81">
       <x:c r="A81" s="33"/>
@@ -1472,6 +3047,24 @@
       <x:c r="D81" s="36" t="n">
         <x:v>20077</x:v>
       </x:c>
+      <x:c r="E81" s="41"/>
+      <x:c r="F81" s="41"/>
+      <x:c r="G81" s="41"/>
+      <x:c r="H81">
+        <x:v>71.50001</x:v>
+      </x:c>
+      <x:c r="I81">
+        <x:v>265.000031</x:v>
+      </x:c>
+      <x:c r="J81">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K81">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L81">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="82">
       <x:c r="A82" s="33"/>
@@ -1484,6 +3077,24 @@
       <x:c r="D82" s="36" t="n">
         <x:v>20078</x:v>
       </x:c>
+      <x:c r="E82" s="41"/>
+      <x:c r="F82" s="41"/>
+      <x:c r="G82" s="41"/>
+      <x:c r="H82">
+        <x:v>175.5</x:v>
+      </x:c>
+      <x:c r="I82">
+        <x:v>238</x:v>
+      </x:c>
+      <x:c r="J82">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K82">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L82">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
     <x:row r="83">
       <x:c r="A83" s="34"/>
@@ -1496,6 +3107,24 @@
       <x:c r="D83" s="37" t="n">
         <x:v>20079</x:v>
       </x:c>
+      <x:c r="E83" s="41"/>
+      <x:c r="F83" s="41"/>
+      <x:c r="G83" s="41"/>
+      <x:c r="H83">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I83">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="J83">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K83">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="L83">
+        <x:v>0</x:v>
+      </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Config/Datas/Tables/g_怪物_MonsterConfig.xlsx
+++ b/Config/Datas/Tables/g_怪物_MonsterConfig.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbMonster" sheetId="1" r:id="Rafbda9c37acc417c"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="TbMonster" sheetId="1" r:id="R5460f4283c264430"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -993,62 +993,45 @@
         </x:is>
       </x:c>
       <x:c r="G1" s="89" t="str">
-        <x:v>bodyRadiusPixelsMilli</x:v>
-      </x:c>
-      <x:c r="H1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        moveRadiusPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        moveHeightPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        moveOffsetXPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        moveOffsetYPixelsMilli</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L1" s="89" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        moveElevationPixelsMilli</x:t>
-        </x:is>
+        <x:v>bodyRadiusPixels</x:v>
+      </x:c>
+      <x:c r="H1" s="89" t="str">
+        <x:v>moveRadiusPixels</x:v>
+      </x:c>
+      <x:c r="I1" s="89" t="str">
+        <x:v>moveHeightPixels</x:v>
+      </x:c>
+      <x:c r="J1" s="89" t="str">
+        <x:v>moveOffsetXPixels</x:v>
+      </x:c>
+      <x:c r="K1" s="89" t="str">
+        <x:v>moveOffsetYPixels</x:v>
+      </x:c>
+      <x:c r="L1" s="89" t="str">
+        <x:v>moveElevationPixels</x:v>
       </x:c>
       <x:c r="M1" s="89" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">movementType</x:t>
         </x:is>
       </x:c>
-      <x:c r="N1" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">damageFloatHeight</x:t>
-        </x:is>
+      <x:c r="N1" t="str">
+        <x:v>damageFloatHeightPixels</x:v>
       </x:c>
       <x:c r="O1" t="str">
-        <x:v>bodyOffsetXPixelsMilli</x:v>
+        <x:v>bodyOffsetXPixels</x:v>
       </x:c>
       <x:c r="P1" t="str">
-        <x:v>bodyOffsetYPixelsMilli</x:v>
+        <x:v>bodyOffsetYPixels</x:v>
       </x:c>
       <x:c r="Q1" t="str">
         <x:v>collisionShape</x:v>
       </x:c>
       <x:c r="R1" t="str">
-        <x:v>hitEffectOffsetXPixelsMilli</x:v>
+        <x:v>hitEffectOffsetXPixels</x:v>
       </x:c>
       <x:c r="S1" t="str">
-        <x:v>hitEffectOffsetYPixelsMilli</x:v>
+        <x:v>hitEffectOffsetYPixels</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="24" customHeight="1">
@@ -1082,66 +1065,46 @@
           <x:t xml:space="preserve">int?#ref=TbSkill</x:t>
         </x:is>
       </x:c>
-      <x:c r="G2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="H2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        int?</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L2" s="92" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        int?</x:t>
-        </x:is>
+      <x:c r="G2" s="92" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="H2" s="92" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="I2" s="92" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="J2" s="92" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="K2" s="92" t="str">
+        <x:v>float?</x:v>
+      </x:c>
+      <x:c r="L2" s="92" t="str">
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="M2" s="92" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">EMovementType?</x:t>
         </x:is>
       </x:c>
-      <x:c r="N2" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">float?</x:t>
-        </x:is>
+      <x:c r="N2" t="str">
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="O2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="P2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="Q2" t="str">
         <x:v>EUnitCollisionShape?</x:v>
       </x:c>
       <x:c r="R2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
       <x:c r="S2" t="str">
-        <x:v>int?</x:v>
+        <x:v>float?</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="22" customHeight="1">
@@ -1200,62 +1163,45 @@
         </x:is>
       </x:c>
       <x:c r="G4" s="101" t="str">
-        <x:v>受击判定半径（像素）；由怪物预制体“受击判定范围”节点导出；像素值×1000存整数，实际值=表值/1000，最多3位小数。</x:v>
-      </x:c>
-      <x:c r="H4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        移动圆柱半径，逻辑像素；由预制体导出；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="I4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        移动圆柱高度，逻辑像素；由预制体导出；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="J4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        圆柱底心横向偏移，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="K4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        圆柱底心地面纵向偏移，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
-      </x:c>
-      <x:c r="L4" s="101" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">
-        圆柱底面离地高度，逻辑像素；原单位×1000存整数，实际值=表值/1000，最多3位小数。</x:t>
-        </x:is>
+        <x:v>受击判定半径；由怪物预制体“受击判定范围”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="H4" s="101" t="str">
+        <x:v>移动圆柱半径；由预制体导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="I4" s="101" t="str">
+        <x:v>移动圆柱高度；由预制体导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="J4" s="101" t="str">
+        <x:v>圆柱底心横向偏移，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="K4" s="101" t="str">
+        <x:v>圆柱底心地面纵向偏移，逻辑像素；直接填写像素值，最多3位小数。</x:v>
+      </x:c>
+      <x:c r="L4" s="101" t="str">
+        <x:v>圆柱底面离地高度，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="M4" s="101" t="inlineStr">
         <x:is>
           <x:t xml:space="preserve">移动分类；正式出战怪必填，资源目录行可空</x:t>
         </x:is>
       </x:c>
-      <x:c r="N4" t="inlineStr">
-        <x:is>
-          <x:t xml:space="preserve">掉血/伤害数字浮动锚点高度（世界单位，Y轴向上）；由预制体 DamageFloatAnchor 节点 localPosition.y 导出；运行时叠加到单位世界坐标上方定位伤害数字。</x:t>
-        </x:is>
+      <x:c r="N4" t="str">
+        <x:v>掉血/伤害数字浮动锚点高度；由预制体 DamageFloatAnchor 节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="O4" t="str">
-        <x:v>受击判定中心横向偏移（像素）；由怪物预制体“受击判定范围”节点导出；像素值×1000存整数。</x:v>
+        <x:v>受击判定中心横向偏移；由怪物预制体“受击判定范围”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="P4" t="str">
-        <x:v>受击判定中心前向偏移（像素）；由怪物预制体“受击判定范围”节点导出；像素值×1000存整数。</x:v>
+        <x:v>受击判定中心前向偏移；由怪物预制体“受击判定范围”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="Q4" t="str">
         <x:v>统一碰撞形状；VerticalCapsule 表示移动阻挡与受击判定共用预制体 CapsuleCollider2D。</x:v>
       </x:c>
       <x:c r="R4" t="str">
-        <x:v>命中特效挂点横向偏移（逻辑像素）；由怪物预制体“命中特效挂点”节点 localPosition.x 导出；像素值×1000存整数。</x:v>
+        <x:v>命中特效挂点横向偏移；由怪物预制体“命中特效挂点”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
       <x:c r="S4" t="str">
-        <x:v>命中特效挂点纵向偏移（逻辑像素）；由怪物预制体“命中特效挂点”节点 localPosition.y 导出；像素值×1000存整数。</x:v>
+        <x:v>命中特效挂点纵向偏移；由怪物预制体“命中特效挂点”节点导出，逻辑像素；直接填写像素值，最多3位小数。</x:v>
       </x:c>
     </x:row>
     <x:row r="5">
@@ -1277,41 +1223,41 @@
       <x:c r="F5" s="77" t="n">
         <x:v>20002</x:v>
       </x:c>
-      <x:c r="G5" s="77">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="H5" s="77">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="I5" s="77">
-        <x:v>149000</x:v>
-      </x:c>
-      <x:c r="J5" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K5" s="77">
-        <x:v>74500</x:v>
-      </x:c>
-      <x:c r="L5" s="77">
+      <x:c r="G5" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H5" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I5" s="77" t="n">
+        <x:v>149</x:v>
+      </x:c>
+      <x:c r="J5" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K5" s="77" t="n">
+        <x:v>74.5</x:v>
+      </x:c>
+      <x:c r="L5" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M5" s="77" t="n"/>
       <x:c r="N5" t="n">
-        <x:v>1.79</x:v>
-      </x:c>
-      <x:c r="O5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P5">
-        <x:v>74500</x:v>
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="O5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P5" t="n">
+        <x:v>74.5</x:v>
       </x:c>
       <x:c r="Q5">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R5">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S5">
+      <x:c r="R5" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S5" t="n">
         <x:v>0</x:v>
       </x:c>
     </x:row>
@@ -1330,42 +1276,42 @@
       </x:c>
       <x:c r="E6" s="77" t="n"/>
       <x:c r="F6" s="77" t="n"/>
-      <x:c r="H6" s="77">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="I6" s="77">
-        <x:v>129000</x:v>
-      </x:c>
-      <x:c r="J6" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K6" s="77">
-        <x:v>64500</x:v>
-      </x:c>
-      <x:c r="L6" s="77">
+      <x:c r="G6" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H6" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I6" s="77" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="J6" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K6" s="77" t="n">
+        <x:v>64.5</x:v>
+      </x:c>
+      <x:c r="L6" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M6" s="77" t="n"/>
       <x:c r="N6" t="n">
-        <x:v>1.59</x:v>
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="O6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P6" t="n">
+        <x:v>64.5</x:v>
       </x:c>
       <x:c r="Q6">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="O6">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P6">
-        <x:v>64500</x:v>
+      <x:c r="R6" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S6" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="7">
@@ -1383,42 +1329,42 @@
       </x:c>
       <x:c r="E7" s="77" t="n"/>
       <x:c r="F7" s="77" t="n"/>
-      <x:c r="H7" s="77">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="I7" s="77">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="J7" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K7" s="77">
-        <x:v>60800</x:v>
-      </x:c>
-      <x:c r="L7" s="77">
+      <x:c r="G7" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H7" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I7" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J7" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K7" s="77" t="n">
+        <x:v>60.8</x:v>
+      </x:c>
+      <x:c r="L7" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M7" s="77" t="n"/>
       <x:c r="N7" t="n">
-        <x:v>2.57</x:v>
+        <x:v>257</x:v>
+      </x:c>
+      <x:c r="O7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P7" t="n">
+        <x:v>60.8</x:v>
       </x:c>
       <x:c r="Q7">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="O7">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P7">
-        <x:v>60800</x:v>
+      <x:c r="R7" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S7" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="8">
@@ -1436,42 +1382,42 @@
       </x:c>
       <x:c r="E8" s="77" t="n"/>
       <x:c r="F8" s="77" t="n"/>
-      <x:c r="H8" s="77">
-        <x:v>28123</x:v>
-      </x:c>
-      <x:c r="I8" s="77">
-        <x:v>120000</x:v>
-      </x:c>
-      <x:c r="J8" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K8" s="77">
-        <x:v>51500</x:v>
-      </x:c>
-      <x:c r="L8" s="77">
+      <x:c r="G8" t="n">
+        <x:v>28.123</x:v>
+      </x:c>
+      <x:c r="H8" s="77" t="n">
+        <x:v>28.123</x:v>
+      </x:c>
+      <x:c r="I8" s="77" t="n">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="J8" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K8" s="77" t="n">
+        <x:v>51.5</x:v>
+      </x:c>
+      <x:c r="L8" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M8" s="77" t="n"/>
       <x:c r="N8" t="n">
-        <x:v>1.59</x:v>
+        <x:v>159</x:v>
+      </x:c>
+      <x:c r="O8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P8" t="n">
+        <x:v>51.5</x:v>
       </x:c>
       <x:c r="Q8">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8">
-        <x:v>28123</x:v>
-      </x:c>
-      <x:c r="O8">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P8">
-        <x:v>51500</x:v>
+      <x:c r="R8" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S8" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="9">
@@ -1489,42 +1435,42 @@
       </x:c>
       <x:c r="E9" s="77" t="n"/>
       <x:c r="F9" s="77" t="n"/>
-      <x:c r="H9" s="77">
-        <x:v>38180</x:v>
-      </x:c>
-      <x:c r="I9" s="77">
-        <x:v>130000</x:v>
-      </x:c>
-      <x:c r="J9" s="77">
-        <x:v>5200</x:v>
-      </x:c>
-      <x:c r="K9" s="77">
-        <x:v>61300</x:v>
-      </x:c>
-      <x:c r="L9" s="77">
+      <x:c r="G9" t="n">
+        <x:v>38.18</x:v>
+      </x:c>
+      <x:c r="H9" s="77" t="n">
+        <x:v>38.18</x:v>
+      </x:c>
+      <x:c r="I9" s="77" t="n">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="J9" s="77" t="n">
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="K9" s="77" t="n">
+        <x:v>61.3</x:v>
+      </x:c>
+      <x:c r="L9" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M9" s="77" t="n"/>
       <x:c r="N9" t="n">
-        <x:v>1.92</x:v>
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="O9" t="n">
+        <x:v>5.2</x:v>
+      </x:c>
+      <x:c r="P9" t="n">
+        <x:v>61.3</x:v>
       </x:c>
       <x:c r="Q9">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S9">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9">
-        <x:v>38180</x:v>
-      </x:c>
-      <x:c r="O9">
-        <x:v>5200</x:v>
-      </x:c>
-      <x:c r="P9">
-        <x:v>61300</x:v>
+      <x:c r="R9" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S9" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="10">
@@ -1542,42 +1488,42 @@
       </x:c>
       <x:c r="E10" s="77" t="n"/>
       <x:c r="F10" s="77" t="n"/>
-      <x:c r="H10" s="77">
-        <x:v>32127</x:v>
-      </x:c>
-      <x:c r="I10" s="77">
-        <x:v>146000</x:v>
-      </x:c>
-      <x:c r="J10" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K10" s="77">
-        <x:v>63600</x:v>
-      </x:c>
-      <x:c r="L10" s="77">
+      <x:c r="G10" t="n">
+        <x:v>32.127</x:v>
+      </x:c>
+      <x:c r="H10" s="77" t="n">
+        <x:v>32.127</x:v>
+      </x:c>
+      <x:c r="I10" s="77" t="n">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="J10" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K10" s="77" t="n">
+        <x:v>63.6</x:v>
+      </x:c>
+      <x:c r="L10" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M10" s="77" t="n"/>
       <x:c r="N10" t="n">
-        <x:v>1.76</x:v>
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="O10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P10" t="n">
+        <x:v>63.6</x:v>
       </x:c>
       <x:c r="Q10">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R10">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S10">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10">
-        <x:v>32127</x:v>
-      </x:c>
-      <x:c r="O10">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P10">
-        <x:v>63600</x:v>
+      <x:c r="R10" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S10" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="11">
@@ -1595,42 +1541,42 @@
       </x:c>
       <x:c r="E11" s="77" t="n"/>
       <x:c r="F11" s="77" t="n"/>
-      <x:c r="H11" s="77">
-        <x:v>69000</x:v>
-      </x:c>
-      <x:c r="I11" s="77">
-        <x:v>145000</x:v>
-      </x:c>
-      <x:c r="J11" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K11" s="77">
-        <x:v>72500</x:v>
-      </x:c>
-      <x:c r="L11" s="77">
+      <x:c r="G11" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H11" s="77" t="n">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="I11" s="77" t="n">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="J11" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K11" s="77" t="n">
+        <x:v>72.5</x:v>
+      </x:c>
+      <x:c r="L11" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M11" s="77" t="n"/>
       <x:c r="N11" t="n">
-        <x:v>1.75</x:v>
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="O11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P11" t="n">
+        <x:v>72.5</x:v>
       </x:c>
       <x:c r="Q11">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11">
-        <x:v>69000</x:v>
-      </x:c>
-      <x:c r="O11">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P11">
-        <x:v>72500</x:v>
+      <x:c r="R11" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S11" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="12">
@@ -1648,42 +1594,42 @@
       </x:c>
       <x:c r="E12" s="77" t="n"/>
       <x:c r="F12" s="77" t="n"/>
-      <x:c r="H12" s="77">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="I12" s="77">
-        <x:v>176000</x:v>
-      </x:c>
-      <x:c r="J12" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K12" s="77">
-        <x:v>88000</x:v>
-      </x:c>
-      <x:c r="L12" s="77">
+      <x:c r="G12" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H12" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I12" s="77" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="J12" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K12" s="77" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="L12" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M12" s="77" t="n"/>
       <x:c r="N12" t="n">
-        <x:v>2.06</x:v>
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="O12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P12" t="n">
+        <x:v>88</x:v>
       </x:c>
       <x:c r="Q12">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R12">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S12">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="O12">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P12">
-        <x:v>88000</x:v>
+      <x:c r="R12" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S12" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="13">
@@ -1701,42 +1647,42 @@
       </x:c>
       <x:c r="E13" s="77" t="n"/>
       <x:c r="F13" s="77" t="n"/>
-      <x:c r="H13" s="77">
-        <x:v>51505</x:v>
-      </x:c>
-      <x:c r="I13" s="77">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="J13" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K13" s="77">
-        <x:v>56600</x:v>
-      </x:c>
-      <x:c r="L13" s="77">
+      <x:c r="G13" t="n">
+        <x:v>51.505</x:v>
+      </x:c>
+      <x:c r="H13" s="77" t="n">
+        <x:v>51.505</x:v>
+      </x:c>
+      <x:c r="I13" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J13" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K13" s="77" t="n">
+        <x:v>56.6</x:v>
+      </x:c>
+      <x:c r="L13" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M13" s="77" t="n"/>
       <x:c r="N13" t="n">
-        <x:v>2</x:v>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="O13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P13" t="n">
+        <x:v>56.6</x:v>
       </x:c>
       <x:c r="Q13">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R13">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S13">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13">
-        <x:v>51505</x:v>
-      </x:c>
-      <x:c r="O13">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P13">
-        <x:v>56600</x:v>
+      <x:c r="R13" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S13" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="14">
@@ -1758,22 +1704,22 @@
       <x:c r="F14" s="77" t="n">
         <x:v>20002</x:v>
       </x:c>
-      <x:c r="G14" s="77">
-        <x:v>44388</x:v>
-      </x:c>
-      <x:c r="H14" s="77">
-        <x:v>44388</x:v>
-      </x:c>
-      <x:c r="I14" s="77">
-        <x:v>88776</x:v>
-      </x:c>
-      <x:c r="J14" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K14" s="77">
-        <x:v>23100</x:v>
-      </x:c>
-      <x:c r="L14" s="77">
+      <x:c r="G14" s="77" t="n">
+        <x:v>44.388</x:v>
+      </x:c>
+      <x:c r="H14" s="77" t="n">
+        <x:v>44.388</x:v>
+      </x:c>
+      <x:c r="I14" s="77" t="n">
+        <x:v>88.776</x:v>
+      </x:c>
+      <x:c r="J14" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K14" s="77" t="n">
+        <x:v>23.1</x:v>
+      </x:c>
+      <x:c r="L14" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M14" s="77" t="inlineStr">
@@ -1782,22 +1728,22 @@
         </x:is>
       </x:c>
       <x:c r="N14" t="n">
-        <x:v>1.1</x:v>
-      </x:c>
-      <x:c r="O14">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P14">
-        <x:v>23100</x:v>
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="O14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P14" t="n">
+        <x:v>23.1</x:v>
       </x:c>
       <x:c r="Q14">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R14">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S14">
-        <x:v>23100</x:v>
+      <x:c r="R14" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S14" t="n">
+        <x:v>23.1</x:v>
       </x:c>
     </x:row>
     <x:row r="15">
@@ -1819,22 +1765,22 @@
       <x:c r="F15" s="77" t="n">
         <x:v>20002</x:v>
       </x:c>
-      <x:c r="G15" s="77">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="H15" s="77">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="I15" s="77">
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="J15" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K15" s="77">
-        <x:v>72000</x:v>
-      </x:c>
-      <x:c r="L15" s="77">
+      <x:c r="G15" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H15" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="I15" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J15" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K15" s="77" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L15" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M15" s="77" t="inlineStr">
@@ -1843,22 +1789,22 @@
         </x:is>
       </x:c>
       <x:c r="N15" t="n">
-        <x:v>1.3</x:v>
-      </x:c>
-      <x:c r="O15">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P15">
-        <x:v>72000</x:v>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="O15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P15" t="n">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="Q15">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R15">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S15">
-        <x:v>72000</x:v>
+      <x:c r="R15" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S15" t="n">
+        <x:v>72</x:v>
       </x:c>
     </x:row>
     <x:row r="16">
@@ -1880,22 +1826,22 @@
       <x:c r="F16" s="77" t="n">
         <x:v>20002</x:v>
       </x:c>
-      <x:c r="G16" s="77">
-        <x:v>28000</x:v>
-      </x:c>
-      <x:c r="H16" s="77">
-        <x:v>28000</x:v>
-      </x:c>
-      <x:c r="I16" s="77">
-        <x:v>111000</x:v>
-      </x:c>
-      <x:c r="J16" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K16" s="77">
-        <x:v>47000</x:v>
-      </x:c>
-      <x:c r="L16" s="77">
+      <x:c r="G16" s="77" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="H16" s="77" t="n">
+        <x:v>28</x:v>
+      </x:c>
+      <x:c r="I16" s="77" t="n">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="J16" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K16" s="77" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="L16" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M16" s="77" t="inlineStr">
@@ -1904,22 +1850,22 @@
         </x:is>
       </x:c>
       <x:c r="N16" t="n">
-        <x:v>1.41</x:v>
-      </x:c>
-      <x:c r="O16">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P16">
-        <x:v>47000</x:v>
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="O16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P16" t="n">
+        <x:v>47</x:v>
       </x:c>
       <x:c r="Q16">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R16">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S16">
-        <x:v>47000</x:v>
+      <x:c r="R16" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S16" t="n">
+        <x:v>47</x:v>
       </x:c>
     </x:row>
     <x:row r="17">
@@ -1941,22 +1887,22 @@
       <x:c r="F17" s="77" t="n">
         <x:v>20002</x:v>
       </x:c>
-      <x:c r="G17" s="77">
-        <x:v>50628</x:v>
-      </x:c>
-      <x:c r="H17" s="77">
-        <x:v>50628</x:v>
-      </x:c>
-      <x:c r="I17" s="77">
-        <x:v>140000</x:v>
-      </x:c>
-      <x:c r="J17" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K17" s="77">
-        <x:v>87000</x:v>
-      </x:c>
-      <x:c r="L17" s="77">
+      <x:c r="G17" s="77" t="n">
+        <x:v>50.628</x:v>
+      </x:c>
+      <x:c r="H17" s="77" t="n">
+        <x:v>50.628</x:v>
+      </x:c>
+      <x:c r="I17" s="77" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="J17" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K17" s="77" t="n">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="L17" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M17" s="77" t="inlineStr">
@@ -1965,22 +1911,22 @@
         </x:is>
       </x:c>
       <x:c r="N17" t="n">
-        <x:v>1.5</x:v>
-      </x:c>
-      <x:c r="O17">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P17">
-        <x:v>87000</x:v>
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="O17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P17" t="n">
+        <x:v>87</x:v>
       </x:c>
       <x:c r="Q17">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R17">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S17">
-        <x:v>87000</x:v>
+      <x:c r="R17" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S17" t="n">
+        <x:v>87</x:v>
       </x:c>
     </x:row>
     <x:row r="18">
@@ -1998,42 +1944,42 @@
       </x:c>
       <x:c r="E18" s="77" t="n"/>
       <x:c r="F18" s="77" t="n"/>
-      <x:c r="H18" s="77">
-        <x:v>51510</x:v>
-      </x:c>
-      <x:c r="I18" s="77">
-        <x:v>160000</x:v>
-      </x:c>
-      <x:c r="J18" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K18" s="77">
-        <x:v>72800</x:v>
-      </x:c>
-      <x:c r="L18" s="77">
+      <x:c r="G18" t="n">
+        <x:v>51.51</x:v>
+      </x:c>
+      <x:c r="H18" s="77" t="n">
+        <x:v>51.51</x:v>
+      </x:c>
+      <x:c r="I18" s="77" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J18" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K18" s="77" t="n">
+        <x:v>72.8</x:v>
+      </x:c>
+      <x:c r="L18" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M18" s="77" t="n"/>
       <x:c r="N18" t="n">
-        <x:v>2.43</x:v>
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="O18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P18" t="n">
+        <x:v>72.8</x:v>
       </x:c>
       <x:c r="Q18">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R18">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S18">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18">
-        <x:v>51510</x:v>
-      </x:c>
-      <x:c r="O18">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P18">
-        <x:v>72800</x:v>
+      <x:c r="R18" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S18" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="19">
@@ -2051,42 +1997,42 @@
       </x:c>
       <x:c r="E19" s="77" t="n"/>
       <x:c r="F19" s="77" t="n"/>
-      <x:c r="H19" s="77">
-        <x:v>70000</x:v>
-      </x:c>
-      <x:c r="I19" s="77">
-        <x:v>172000</x:v>
-      </x:c>
-      <x:c r="J19" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K19" s="77">
-        <x:v>65200</x:v>
-      </x:c>
-      <x:c r="L19" s="77">
+      <x:c r="G19" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H19" s="77" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="I19" s="77" t="n">
+        <x:v>172</x:v>
+      </x:c>
+      <x:c r="J19" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K19" s="77" t="n">
+        <x:v>65.2</x:v>
+      </x:c>
+      <x:c r="L19" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M19" s="77" t="n"/>
       <x:c r="N19" t="n">
-        <x:v>2.02</x:v>
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="O19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P19" t="n">
+        <x:v>65.2</x:v>
       </x:c>
       <x:c r="Q19">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R19">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S19">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19">
-        <x:v>70000</x:v>
-      </x:c>
-      <x:c r="O19">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P19">
-        <x:v>65200</x:v>
+      <x:c r="R19" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S19" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20">
@@ -2104,42 +2050,42 @@
       </x:c>
       <x:c r="E20" s="77" t="n"/>
       <x:c r="F20" s="77" t="n"/>
-      <x:c r="H20" s="77">
-        <x:v>44142</x:v>
-      </x:c>
-      <x:c r="I20" s="77">
-        <x:v>158000</x:v>
-      </x:c>
-      <x:c r="J20" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K20" s="77">
-        <x:v>63200</x:v>
-      </x:c>
-      <x:c r="L20" s="77">
+      <x:c r="G20" t="n">
+        <x:v>44.142</x:v>
+      </x:c>
+      <x:c r="H20" s="77" t="n">
+        <x:v>44.142</x:v>
+      </x:c>
+      <x:c r="I20" s="77" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J20" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K20" s="77" t="n">
+        <x:v>63.2</x:v>
+      </x:c>
+      <x:c r="L20" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M20" s="77" t="n"/>
       <x:c r="N20" t="n">
-        <x:v>1.88</x:v>
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="O20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P20" t="n">
+        <x:v>63.2</x:v>
       </x:c>
       <x:c r="Q20">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R20">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S20">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20">
-        <x:v>44142</x:v>
-      </x:c>
-      <x:c r="O20">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P20">
-        <x:v>63200</x:v>
+      <x:c r="R20" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S20" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="21">
@@ -2157,42 +2103,42 @@
       </x:c>
       <x:c r="E21" s="77" t="n"/>
       <x:c r="F21" s="77" t="n"/>
-      <x:c r="H21" s="77">
-        <x:v>79000</x:v>
-      </x:c>
-      <x:c r="I21" s="77">
-        <x:v>170000</x:v>
-      </x:c>
-      <x:c r="J21" s="77">
-        <x:v>-15100</x:v>
-      </x:c>
-      <x:c r="K21" s="77">
-        <x:v>74600</x:v>
-      </x:c>
-      <x:c r="L21" s="77">
+      <x:c r="G21" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H21" s="77" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I21" s="77" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J21" s="77" t="n">
+        <x:v>-15.1</x:v>
+      </x:c>
+      <x:c r="K21" s="77" t="n">
+        <x:v>74.6</x:v>
+      </x:c>
+      <x:c r="L21" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M21" s="77" t="n"/>
       <x:c r="N21" t="n">
-        <x:v>2</x:v>
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="O21" t="n">
+        <x:v>-15.1</x:v>
+      </x:c>
+      <x:c r="P21" t="n">
+        <x:v>74.6</x:v>
       </x:c>
       <x:c r="Q21">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R21">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S21">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21">
-        <x:v>79000</x:v>
-      </x:c>
-      <x:c r="O21">
-        <x:v>-15100</x:v>
-      </x:c>
-      <x:c r="P21">
-        <x:v>74600</x:v>
+      <x:c r="R21" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S21" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="22">
@@ -2210,42 +2156,42 @@
       </x:c>
       <x:c r="E22" s="77" t="n"/>
       <x:c r="F22" s="77" t="n"/>
-      <x:c r="H22" s="77">
-        <x:v>47500</x:v>
-      </x:c>
-      <x:c r="I22" s="77">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="J22" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K22" s="77">
-        <x:v>68300</x:v>
-      </x:c>
-      <x:c r="L22" s="77">
+      <x:c r="G22" t="n">
+        <x:v>47.5</x:v>
+      </x:c>
+      <x:c r="H22" s="77" t="n">
+        <x:v>47.5</x:v>
+      </x:c>
+      <x:c r="I22" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J22" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K22" s="77" t="n">
+        <x:v>68.3</x:v>
+      </x:c>
+      <x:c r="L22" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M22" s="77" t="n"/>
       <x:c r="N22" t="n">
-        <x:v>2.28</x:v>
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="O22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P22" t="n">
+        <x:v>68.3</x:v>
       </x:c>
       <x:c r="Q22">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R22">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S22">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22">
-        <x:v>47500</x:v>
-      </x:c>
-      <x:c r="O22">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P22">
-        <x:v>68300</x:v>
+      <x:c r="R22" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S22" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23">
@@ -2263,42 +2209,42 @@
       </x:c>
       <x:c r="E23" s="77" t="n"/>
       <x:c r="F23" s="77" t="n"/>
-      <x:c r="H23" s="77">
-        <x:v>48915</x:v>
-      </x:c>
-      <x:c r="I23" s="77">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="J23" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K23" s="77">
-        <x:v>61900</x:v>
-      </x:c>
-      <x:c r="L23" s="77">
+      <x:c r="G23" t="n">
+        <x:v>48.915</x:v>
+      </x:c>
+      <x:c r="H23" s="77" t="n">
+        <x:v>48.915</x:v>
+      </x:c>
+      <x:c r="I23" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J23" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K23" s="77" t="n">
+        <x:v>61.9</x:v>
+      </x:c>
+      <x:c r="L23" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M23" s="77" t="n"/>
       <x:c r="N23" t="n">
-        <x:v>2.09</x:v>
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="O23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P23" t="n">
+        <x:v>61.9</x:v>
       </x:c>
       <x:c r="Q23">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R23">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S23">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23">
-        <x:v>48915</x:v>
-      </x:c>
-      <x:c r="O23">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P23">
-        <x:v>61900</x:v>
+      <x:c r="R23" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S23" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="24">
@@ -2316,42 +2262,42 @@
       </x:c>
       <x:c r="E24" s="77" t="n"/>
       <x:c r="F24" s="77" t="n"/>
-      <x:c r="H24" s="77">
-        <x:v>51000</x:v>
-      </x:c>
-      <x:c r="I24" s="77">
-        <x:v>158000</x:v>
-      </x:c>
-      <x:c r="J24" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K24" s="77">
-        <x:v>79000</x:v>
-      </x:c>
-      <x:c r="L24" s="77">
+      <x:c r="G24" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="H24" s="77" t="n">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="I24" s="77" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J24" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K24" s="77" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="L24" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M24" s="77" t="n"/>
       <x:c r="N24" t="n">
-        <x:v>1.88</x:v>
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="O24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P24" t="n">
+        <x:v>79</x:v>
       </x:c>
       <x:c r="Q24">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R24">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S24">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24">
-        <x:v>51000</x:v>
-      </x:c>
-      <x:c r="O24">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P24">
-        <x:v>79000</x:v>
+      <x:c r="R24" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S24" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25">
@@ -2369,42 +2315,42 @@
       </x:c>
       <x:c r="E25" s="77" t="n"/>
       <x:c r="F25" s="77" t="n"/>
-      <x:c r="H25" s="77">
-        <x:v>78000</x:v>
-      </x:c>
-      <x:c r="I25" s="77">
-        <x:v>156000</x:v>
-      </x:c>
-      <x:c r="J25" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K25" s="77">
-        <x:v>67500</x:v>
-      </x:c>
-      <x:c r="L25" s="77">
+      <x:c r="G25" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H25" s="77" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="I25" s="77" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="J25" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K25" s="77" t="n">
+        <x:v>67.5</x:v>
+      </x:c>
+      <x:c r="L25" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M25" s="77" t="n"/>
       <x:c r="N25" t="n">
-        <x:v>1.65</x:v>
+        <x:v>165</x:v>
+      </x:c>
+      <x:c r="O25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P25" t="n">
+        <x:v>67.5</x:v>
       </x:c>
       <x:c r="Q25">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R25">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S25">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25">
-        <x:v>78000</x:v>
-      </x:c>
-      <x:c r="O25">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P25">
-        <x:v>67500</x:v>
+      <x:c r="R25" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S25" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="26">
@@ -2422,42 +2368,42 @@
       </x:c>
       <x:c r="E26" s="77" t="n"/>
       <x:c r="F26" s="77" t="n"/>
-      <x:c r="H26" s="77">
-        <x:v>73310</x:v>
-      </x:c>
-      <x:c r="I26" s="77">
-        <x:v>146620</x:v>
-      </x:c>
-      <x:c r="J26" s="77">
-        <x:v>-26000</x:v>
-      </x:c>
-      <x:c r="K26" s="77">
-        <x:v>53000</x:v>
-      </x:c>
-      <x:c r="L26" s="77">
+      <x:c r="G26" t="n">
+        <x:v>73.31</x:v>
+      </x:c>
+      <x:c r="H26" s="77" t="n">
+        <x:v>73.31</x:v>
+      </x:c>
+      <x:c r="I26" s="77" t="n">
+        <x:v>146.62</x:v>
+      </x:c>
+      <x:c r="J26" s="77" t="n">
+        <x:v>-26</x:v>
+      </x:c>
+      <x:c r="K26" s="77" t="n">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="L26" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M26" s="77" t="n"/>
       <x:c r="N26" t="n">
-        <x:v>2.18</x:v>
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="O26" t="n">
+        <x:v>-26</x:v>
+      </x:c>
+      <x:c r="P26" t="n">
+        <x:v>53</x:v>
       </x:c>
       <x:c r="Q26">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R26">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S26">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G26">
-        <x:v>73310</x:v>
-      </x:c>
-      <x:c r="O26">
-        <x:v>-26000</x:v>
-      </x:c>
-      <x:c r="P26">
-        <x:v>53000</x:v>
+      <x:c r="R26" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S26" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="27">
@@ -2475,42 +2421,42 @@
       </x:c>
       <x:c r="E27" s="77" t="n"/>
       <x:c r="F27" s="77" t="n"/>
-      <x:c r="H27" s="77">
-        <x:v>75197</x:v>
-      </x:c>
-      <x:c r="I27" s="77">
-        <x:v>170000</x:v>
-      </x:c>
-      <x:c r="J27" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K27" s="77">
-        <x:v>84500</x:v>
-      </x:c>
-      <x:c r="L27" s="77">
+      <x:c r="G27" t="n">
+        <x:v>75.197</x:v>
+      </x:c>
+      <x:c r="H27" s="77" t="n">
+        <x:v>75.197</x:v>
+      </x:c>
+      <x:c r="I27" s="77" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J27" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K27" s="77" t="n">
+        <x:v>84.5</x:v>
+      </x:c>
+      <x:c r="L27" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M27" s="77" t="n"/>
       <x:c r="N27" t="n">
-        <x:v>2.82</x:v>
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="O27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P27" t="n">
+        <x:v>84.5</x:v>
       </x:c>
       <x:c r="Q27">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R27">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S27">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G27">
-        <x:v>75197</x:v>
-      </x:c>
-      <x:c r="O27">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P27">
-        <x:v>84500</x:v>
+      <x:c r="R27" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S27" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="28">
@@ -2528,42 +2474,42 @@
       </x:c>
       <x:c r="E28" s="77" t="n"/>
       <x:c r="F28" s="77" t="n"/>
-      <x:c r="H28" s="77">
-        <x:v>63098</x:v>
-      </x:c>
-      <x:c r="I28" s="77">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="J28" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K28" s="77">
-        <x:v>75000</x:v>
-      </x:c>
-      <x:c r="L28" s="77">
+      <x:c r="G28" t="n">
+        <x:v>63.098</x:v>
+      </x:c>
+      <x:c r="H28" s="77" t="n">
+        <x:v>63.098</x:v>
+      </x:c>
+      <x:c r="I28" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J28" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K28" s="77" t="n">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="L28" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M28" s="77" t="n"/>
       <x:c r="N28" t="n">
-        <x:v>2.33</x:v>
+        <x:v>233</x:v>
+      </x:c>
+      <x:c r="O28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P28" t="n">
+        <x:v>75</x:v>
       </x:c>
       <x:c r="Q28">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R28">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S28">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G28">
-        <x:v>63098</x:v>
-      </x:c>
-      <x:c r="O28">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P28">
-        <x:v>75000</x:v>
+      <x:c r="R28" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S28" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="29">
@@ -2581,42 +2527,42 @@
       </x:c>
       <x:c r="E29" s="77" t="n"/>
       <x:c r="F29" s="77" t="n"/>
-      <x:c r="H29" s="77">
-        <x:v>67081</x:v>
-      </x:c>
-      <x:c r="I29" s="77">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="J29" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K29" s="77">
-        <x:v>70000</x:v>
-      </x:c>
-      <x:c r="L29" s="77">
+      <x:c r="G29" t="n">
+        <x:v>67.081</x:v>
+      </x:c>
+      <x:c r="H29" s="77" t="n">
+        <x:v>67.081</x:v>
+      </x:c>
+      <x:c r="I29" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J29" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K29" s="77" t="n">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="L29" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M29" s="77" t="n"/>
       <x:c r="N29" t="n">
-        <x:v>2.28</x:v>
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="O29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P29" t="n">
+        <x:v>70</x:v>
       </x:c>
       <x:c r="Q29">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R29">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S29">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G29">
-        <x:v>67081</x:v>
-      </x:c>
-      <x:c r="O29">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P29">
-        <x:v>70000</x:v>
+      <x:c r="R29" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S29" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="30">
@@ -2634,42 +2580,42 @@
       </x:c>
       <x:c r="E30" s="77" t="n"/>
       <x:c r="F30" s="77" t="n"/>
-      <x:c r="H30" s="77">
-        <x:v>54500</x:v>
-      </x:c>
-      <x:c r="I30" s="77">
-        <x:v>141000</x:v>
-      </x:c>
-      <x:c r="J30" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K30" s="77">
-        <x:v>56700</x:v>
-      </x:c>
-      <x:c r="L30" s="77">
+      <x:c r="G30" t="n">
+        <x:v>54.5</x:v>
+      </x:c>
+      <x:c r="H30" s="77" t="n">
+        <x:v>54.5</x:v>
+      </x:c>
+      <x:c r="I30" s="77" t="n">
+        <x:v>141</x:v>
+      </x:c>
+      <x:c r="J30" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K30" s="77" t="n">
+        <x:v>56.7</x:v>
+      </x:c>
+      <x:c r="L30" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M30" s="77" t="n"/>
       <x:c r="N30" t="n">
-        <x:v>1.71</x:v>
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="O30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P30" t="n">
+        <x:v>56.7</x:v>
       </x:c>
       <x:c r="Q30">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R30">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S30">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G30">
-        <x:v>54500</x:v>
-      </x:c>
-      <x:c r="O30">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P30">
-        <x:v>56700</x:v>
+      <x:c r="R30" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S30" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="31">
@@ -2687,42 +2633,42 @@
       </x:c>
       <x:c r="E31" s="77" t="n"/>
       <x:c r="F31" s="77" t="n"/>
-      <x:c r="H31" s="77">
-        <x:v>41000</x:v>
-      </x:c>
-      <x:c r="I31" s="77">
-        <x:v>158000</x:v>
-      </x:c>
-      <x:c r="J31" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K31" s="77">
-        <x:v>63900</x:v>
-      </x:c>
-      <x:c r="L31" s="77">
+      <x:c r="G31" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="H31" s="77" t="n">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I31" s="77" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J31" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K31" s="77" t="n">
+        <x:v>63.9</x:v>
+      </x:c>
+      <x:c r="L31" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M31" s="77" t="n"/>
       <x:c r="N31" t="n">
-        <x:v>1.88</x:v>
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="O31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P31" t="n">
+        <x:v>63.9</x:v>
       </x:c>
       <x:c r="Q31">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R31">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S31">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G31">
-        <x:v>41000</x:v>
-      </x:c>
-      <x:c r="O31">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P31">
-        <x:v>63900</x:v>
+      <x:c r="R31" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S31" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="32">
@@ -2740,42 +2686,42 @@
       </x:c>
       <x:c r="E32" s="77" t="n"/>
       <x:c r="F32" s="77" t="n"/>
-      <x:c r="H32" s="77">
-        <x:v>51499</x:v>
-      </x:c>
-      <x:c r="I32" s="77">
-        <x:v>183000</x:v>
-      </x:c>
-      <x:c r="J32" s="77">
-        <x:v>-12000</x:v>
-      </x:c>
-      <x:c r="K32" s="77">
-        <x:v>84000</x:v>
-      </x:c>
-      <x:c r="L32" s="77">
+      <x:c r="G32" t="n">
+        <x:v>51.499</x:v>
+      </x:c>
+      <x:c r="H32" s="77" t="n">
+        <x:v>51.499</x:v>
+      </x:c>
+      <x:c r="I32" s="77" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J32" s="77" t="n">
+        <x:v>-12</x:v>
+      </x:c>
+      <x:c r="K32" s="77" t="n">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="L32" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M32" s="77" t="n"/>
       <x:c r="N32" t="n">
-        <x:v>2.13</x:v>
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="O32" t="n">
+        <x:v>-12</x:v>
+      </x:c>
+      <x:c r="P32" t="n">
+        <x:v>84</x:v>
       </x:c>
       <x:c r="Q32">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R32">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S32">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G32">
-        <x:v>51499</x:v>
-      </x:c>
-      <x:c r="O32">
-        <x:v>-12000</x:v>
-      </x:c>
-      <x:c r="P32">
-        <x:v>84000</x:v>
+      <x:c r="R32" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S32" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="33">
@@ -2793,42 +2739,42 @@
       </x:c>
       <x:c r="E33" s="77" t="n"/>
       <x:c r="F33" s="77" t="n"/>
-      <x:c r="H33" s="77">
-        <x:v>43500</x:v>
-      </x:c>
-      <x:c r="I33" s="77">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="J33" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K33" s="77">
-        <x:v>67200</x:v>
-      </x:c>
-      <x:c r="L33" s="77">
+      <x:c r="G33" t="n">
+        <x:v>43.5</x:v>
+      </x:c>
+      <x:c r="H33" s="77" t="n">
+        <x:v>43.5</x:v>
+      </x:c>
+      <x:c r="I33" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J33" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K33" s="77" t="n">
+        <x:v>67.2</x:v>
+      </x:c>
+      <x:c r="L33" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M33" s="77" t="n"/>
       <x:c r="N33" t="n">
-        <x:v>2.17</x:v>
+        <x:v>217</x:v>
+      </x:c>
+      <x:c r="O33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P33" t="n">
+        <x:v>67.2</x:v>
       </x:c>
       <x:c r="Q33">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R33">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S33">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G33">
-        <x:v>43500</x:v>
-      </x:c>
-      <x:c r="O33">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P33">
-        <x:v>67200</x:v>
+      <x:c r="R33" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S33" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="34">
@@ -2846,42 +2792,42 @@
       </x:c>
       <x:c r="E34" s="77" t="n"/>
       <x:c r="F34" s="77" t="n"/>
-      <x:c r="H34" s="77">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="I34" s="77">
-        <x:v>147000</x:v>
-      </x:c>
-      <x:c r="J34" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K34" s="77">
-        <x:v>73500</x:v>
-      </x:c>
-      <x:c r="L34" s="77">
+      <x:c r="G34" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="H34" s="77" t="n">
+        <x:v>45</x:v>
+      </x:c>
+      <x:c r="I34" s="77" t="n">
+        <x:v>147</x:v>
+      </x:c>
+      <x:c r="J34" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K34" s="77" t="n">
+        <x:v>73.5</x:v>
+      </x:c>
+      <x:c r="L34" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M34" s="77" t="n"/>
       <x:c r="N34" t="n">
-        <x:v>1.77</x:v>
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="O34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P34" t="n">
+        <x:v>73.5</x:v>
       </x:c>
       <x:c r="Q34">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R34">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S34">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G34">
-        <x:v>45000</x:v>
-      </x:c>
-      <x:c r="O34">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P34">
-        <x:v>73500</x:v>
+      <x:c r="R34" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S34" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="35">
@@ -2899,42 +2845,42 @@
       </x:c>
       <x:c r="E35" s="77" t="n"/>
       <x:c r="F35" s="77" t="n"/>
-      <x:c r="H35" s="77">
-        <x:v>79000</x:v>
-      </x:c>
-      <x:c r="I35" s="77">
-        <x:v>158000</x:v>
-      </x:c>
-      <x:c r="J35" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K35" s="77">
-        <x:v>61500</x:v>
-      </x:c>
-      <x:c r="L35" s="77">
+      <x:c r="G35" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H35" s="77" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I35" s="77" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J35" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K35" s="77" t="n">
+        <x:v>61.5</x:v>
+      </x:c>
+      <x:c r="L35" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M35" s="77" t="n"/>
       <x:c r="N35" t="n">
-        <x:v>1.85</x:v>
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="O35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P35" t="n">
+        <x:v>61.5</x:v>
       </x:c>
       <x:c r="Q35">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R35">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S35">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G35">
-        <x:v>79000</x:v>
-      </x:c>
-      <x:c r="O35">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P35">
-        <x:v>61500</x:v>
+      <x:c r="R35" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S35" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="36">
@@ -2956,22 +2902,22 @@
       <x:c r="F36" s="77" t="n">
         <x:v>20002</x:v>
       </x:c>
-      <x:c r="G36" s="77">
-        <x:v>73011</x:v>
-      </x:c>
-      <x:c r="H36" s="77">
-        <x:v>73011</x:v>
-      </x:c>
-      <x:c r="I36" s="77">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="J36" s="77">
-        <x:v>-9400</x:v>
-      </x:c>
-      <x:c r="K36" s="77">
-        <x:v>80200</x:v>
-      </x:c>
-      <x:c r="L36" s="77">
+      <x:c r="G36" s="77" t="n">
+        <x:v>73.011</x:v>
+      </x:c>
+      <x:c r="H36" s="77" t="n">
+        <x:v>73.011</x:v>
+      </x:c>
+      <x:c r="I36" s="77" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J36" s="77" t="n">
+        <x:v>-9.4</x:v>
+      </x:c>
+      <x:c r="K36" s="77" t="n">
+        <x:v>80.2</x:v>
+      </x:c>
+      <x:c r="L36" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M36" s="77" t="inlineStr">
@@ -2980,22 +2926,22 @@
         </x:is>
       </x:c>
       <x:c r="N36" t="n">
-        <x:v>2.83</x:v>
-      </x:c>
-      <x:c r="O36">
-        <x:v>-9400</x:v>
-      </x:c>
-      <x:c r="P36">
-        <x:v>80200</x:v>
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="O36" t="n">
+        <x:v>-9.4</x:v>
+      </x:c>
+      <x:c r="P36" t="n">
+        <x:v>80.2</x:v>
       </x:c>
       <x:c r="Q36">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R36">
-        <x:v>-9400</x:v>
-      </x:c>
-      <x:c r="S36">
-        <x:v>80200</x:v>
+      <x:c r="R36" t="n">
+        <x:v>-9.4</x:v>
+      </x:c>
+      <x:c r="S36" t="n">
+        <x:v>80.2</x:v>
       </x:c>
     </x:row>
     <x:row r="37">
@@ -3013,42 +2959,42 @@
       </x:c>
       <x:c r="E37" s="77" t="n"/>
       <x:c r="F37" s="77" t="n"/>
-      <x:c r="H37" s="77">
-        <x:v>72000</x:v>
-      </x:c>
-      <x:c r="I37" s="77">
-        <x:v>180000</x:v>
-      </x:c>
-      <x:c r="J37" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K37" s="77">
-        <x:v>72000</x:v>
-      </x:c>
-      <x:c r="L37" s="77">
+      <x:c r="G37" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H37" s="77" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="I37" s="77" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J37" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K37" s="77" t="n">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="L37" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M37" s="77" t="n"/>
       <x:c r="N37" t="n">
-        <x:v>2.46</x:v>
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="O37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P37" t="n">
+        <x:v>72</x:v>
       </x:c>
       <x:c r="Q37">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R37">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S37">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G37">
-        <x:v>72000</x:v>
-      </x:c>
-      <x:c r="O37">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P37">
-        <x:v>72000</x:v>
+      <x:c r="R37" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S37" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="38">
@@ -3066,42 +3012,42 @@
       </x:c>
       <x:c r="E38" s="77" t="n"/>
       <x:c r="F38" s="77" t="n"/>
-      <x:c r="H38" s="77">
-        <x:v>62500</x:v>
-      </x:c>
-      <x:c r="I38" s="77">
-        <x:v>195000</x:v>
-      </x:c>
-      <x:c r="J38" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K38" s="77">
-        <x:v>97500</x:v>
-      </x:c>
-      <x:c r="L38" s="77">
+      <x:c r="G38" t="n">
+        <x:v>62.5</x:v>
+      </x:c>
+      <x:c r="H38" s="77" t="n">
+        <x:v>62.5</x:v>
+      </x:c>
+      <x:c r="I38" s="77" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J38" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K38" s="77" t="n">
+        <x:v>97.5</x:v>
+      </x:c>
+      <x:c r="L38" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M38" s="77" t="n"/>
       <x:c r="N38" t="n">
-        <x:v>2.25</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="O38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P38" t="n">
+        <x:v>97.5</x:v>
       </x:c>
       <x:c r="Q38">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R38">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S38">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G38">
-        <x:v>62500</x:v>
-      </x:c>
-      <x:c r="O38">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P38">
-        <x:v>97500</x:v>
+      <x:c r="R38" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S38" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="39">
@@ -3119,42 +3065,42 @@
       </x:c>
       <x:c r="E39" s="77" t="n"/>
       <x:c r="F39" s="77" t="n"/>
-      <x:c r="H39" s="77">
-        <x:v>52482</x:v>
-      </x:c>
-      <x:c r="I39" s="77">
-        <x:v>158000</x:v>
-      </x:c>
-      <x:c r="J39" s="77">
-        <x:v>-2000</x:v>
-      </x:c>
-      <x:c r="K39" s="77">
-        <x:v>62000</x:v>
-      </x:c>
-      <x:c r="L39" s="77">
+      <x:c r="G39" t="n">
+        <x:v>52.482</x:v>
+      </x:c>
+      <x:c r="H39" s="77" t="n">
+        <x:v>52.482</x:v>
+      </x:c>
+      <x:c r="I39" s="77" t="n">
+        <x:v>158</x:v>
+      </x:c>
+      <x:c r="J39" s="77" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="K39" s="77" t="n">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="L39" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M39" s="77" t="n"/>
       <x:c r="N39" t="n">
-        <x:v>1.88</x:v>
+        <x:v>188</x:v>
+      </x:c>
+      <x:c r="O39" t="n">
+        <x:v>-2</x:v>
+      </x:c>
+      <x:c r="P39" t="n">
+        <x:v>62</x:v>
       </x:c>
       <x:c r="Q39">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R39">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S39">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G39">
-        <x:v>52482</x:v>
-      </x:c>
-      <x:c r="O39">
-        <x:v>-2000</x:v>
-      </x:c>
-      <x:c r="P39">
-        <x:v>62000</x:v>
+      <x:c r="R39" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S39" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="40">
@@ -3172,42 +3118,42 @@
       </x:c>
       <x:c r="E40" s="77" t="n"/>
       <x:c r="F40" s="77" t="n"/>
-      <x:c r="H40" s="77">
-        <x:v>67000</x:v>
-      </x:c>
-      <x:c r="I40" s="77">
-        <x:v>170000</x:v>
-      </x:c>
-      <x:c r="J40" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K40" s="77">
-        <x:v>74800</x:v>
-      </x:c>
-      <x:c r="L40" s="77">
+      <x:c r="G40" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="H40" s="77" t="n">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="I40" s="77" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J40" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K40" s="77" t="n">
+        <x:v>74.8</x:v>
+      </x:c>
+      <x:c r="L40" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M40" s="77" t="n"/>
       <x:c r="N40" t="n">
-        <x:v>2.27</x:v>
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="O40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P40" t="n">
+        <x:v>74.8</x:v>
       </x:c>
       <x:c r="Q40">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R40">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S40">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G40">
-        <x:v>67000</x:v>
-      </x:c>
-      <x:c r="O40">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P40">
-        <x:v>74800</x:v>
+      <x:c r="R40" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S40" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="41">
@@ -3225,42 +3171,42 @@
       </x:c>
       <x:c r="E41" s="77" t="n"/>
       <x:c r="F41" s="77" t="n"/>
-      <x:c r="H41" s="77">
-        <x:v>59500</x:v>
-      </x:c>
-      <x:c r="I41" s="77">
-        <x:v>140000</x:v>
-      </x:c>
-      <x:c r="J41" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K41" s="77">
-        <x:v>51800</x:v>
-      </x:c>
-      <x:c r="L41" s="77">
+      <x:c r="G41" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="H41" s="77" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="I41" s="77" t="n">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="J41" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K41" s="77" t="n">
+        <x:v>51.8</x:v>
+      </x:c>
+      <x:c r="L41" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M41" s="77" t="n"/>
       <x:c r="N41" t="n">
-        <x:v>2.09</x:v>
+        <x:v>209</x:v>
+      </x:c>
+      <x:c r="O41" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P41" t="n">
+        <x:v>51.8</x:v>
       </x:c>
       <x:c r="Q41">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R41">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S41">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G41">
-        <x:v>59500</x:v>
-      </x:c>
-      <x:c r="O41">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P41">
-        <x:v>51800</x:v>
+      <x:c r="R41" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S41" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="42">
@@ -3278,42 +3224,42 @@
       </x:c>
       <x:c r="E42" s="77" t="n"/>
       <x:c r="F42" s="77" t="n"/>
-      <x:c r="H42" s="77">
-        <x:v>49614</x:v>
-      </x:c>
-      <x:c r="I42" s="77">
-        <x:v>173000</x:v>
-      </x:c>
-      <x:c r="J42" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K42" s="77">
-        <x:v>67900</x:v>
-      </x:c>
-      <x:c r="L42" s="77">
+      <x:c r="G42" t="n">
+        <x:v>49.614</x:v>
+      </x:c>
+      <x:c r="H42" s="77" t="n">
+        <x:v>49.614</x:v>
+      </x:c>
+      <x:c r="I42" s="77" t="n">
+        <x:v>173</x:v>
+      </x:c>
+      <x:c r="J42" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K42" s="77" t="n">
+        <x:v>67.9</x:v>
+      </x:c>
+      <x:c r="L42" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M42" s="77" t="n"/>
       <x:c r="N42" t="n">
-        <x:v>2.03</x:v>
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="O42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P42" t="n">
+        <x:v>67.9</x:v>
       </x:c>
       <x:c r="Q42">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R42">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S42">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G42">
-        <x:v>49614</x:v>
-      </x:c>
-      <x:c r="O42">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P42">
-        <x:v>67900</x:v>
+      <x:c r="R42" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S42" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="43">
@@ -3331,42 +3277,42 @@
       </x:c>
       <x:c r="E43" s="77" t="n"/>
       <x:c r="F43" s="77" t="n"/>
-      <x:c r="H43" s="77">
-        <x:v>54467</x:v>
-      </x:c>
-      <x:c r="I43" s="77">
-        <x:v>154000</x:v>
-      </x:c>
-      <x:c r="J43" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K43" s="77">
-        <x:v>57700</x:v>
-      </x:c>
-      <x:c r="L43" s="77">
+      <x:c r="G43" t="n">
+        <x:v>54.467</x:v>
+      </x:c>
+      <x:c r="H43" s="77" t="n">
+        <x:v>54.467</x:v>
+      </x:c>
+      <x:c r="I43" s="77" t="n">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="J43" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K43" s="77" t="n">
+        <x:v>57.7</x:v>
+      </x:c>
+      <x:c r="L43" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M43" s="77" t="n"/>
       <x:c r="N43" t="n">
-        <x:v>1.84</x:v>
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="O43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P43" t="n">
+        <x:v>57.7</x:v>
       </x:c>
       <x:c r="Q43">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R43">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S43">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G43">
-        <x:v>54467</x:v>
-      </x:c>
-      <x:c r="O43">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P43">
-        <x:v>57700</x:v>
+      <x:c r="R43" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S43" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="44">
@@ -3384,42 +3330,42 @@
       </x:c>
       <x:c r="E44" s="77" t="n"/>
       <x:c r="F44" s="77" t="n"/>
-      <x:c r="H44" s="77">
-        <x:v>64500</x:v>
-      </x:c>
-      <x:c r="I44" s="77">
-        <x:v>220000</x:v>
-      </x:c>
-      <x:c r="J44" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K44" s="77">
-        <x:v>80100</x:v>
-      </x:c>
-      <x:c r="L44" s="77">
+      <x:c r="G44" t="n">
+        <x:v>64.5</x:v>
+      </x:c>
+      <x:c r="H44" s="77" t="n">
+        <x:v>64.5</x:v>
+      </x:c>
+      <x:c r="I44" s="77" t="n">
+        <x:v>220</x:v>
+      </x:c>
+      <x:c r="J44" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K44" s="77" t="n">
+        <x:v>80.1</x:v>
+      </x:c>
+      <x:c r="L44" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M44" s="77" t="n"/>
       <x:c r="N44" t="n">
-        <x:v>2.84</x:v>
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="O44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P44" t="n">
+        <x:v>80.1</x:v>
       </x:c>
       <x:c r="Q44">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R44">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S44">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G44">
-        <x:v>64500</x:v>
-      </x:c>
-      <x:c r="O44">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P44">
-        <x:v>80100</x:v>
+      <x:c r="R44" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S44" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="45">
@@ -3437,42 +3383,42 @@
       </x:c>
       <x:c r="E45" s="77" t="n"/>
       <x:c r="F45" s="77" t="n"/>
-      <x:c r="H45" s="77">
-        <x:v>55500</x:v>
-      </x:c>
-      <x:c r="I45" s="77">
-        <x:v>200000</x:v>
-      </x:c>
-      <x:c r="J45" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K45" s="77">
-        <x:v>61000</x:v>
-      </x:c>
-      <x:c r="L45" s="77">
+      <x:c r="G45" t="n">
+        <x:v>55.5</x:v>
+      </x:c>
+      <x:c r="H45" s="77" t="n">
+        <x:v>55.5</x:v>
+      </x:c>
+      <x:c r="I45" s="77" t="n">
+        <x:v>200</x:v>
+      </x:c>
+      <x:c r="J45" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K45" s="77" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L45" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M45" s="77" t="n"/>
       <x:c r="N45" t="n">
-        <x:v>2.48</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="O45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P45" t="n">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Q45">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R45">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S45">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G45">
-        <x:v>55500</x:v>
-      </x:c>
-      <x:c r="O45">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P45">
-        <x:v>61000</x:v>
+      <x:c r="R45" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S45" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="46">
@@ -3490,42 +3436,42 @@
       </x:c>
       <x:c r="E46" s="77" t="n"/>
       <x:c r="F46" s="77" t="n"/>
-      <x:c r="H46" s="77">
-        <x:v>79000</x:v>
-      </x:c>
-      <x:c r="I46" s="77">
-        <x:v>169000</x:v>
-      </x:c>
-      <x:c r="J46" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K46" s="77">
-        <x:v>84500</x:v>
-      </x:c>
-      <x:c r="L46" s="77">
+      <x:c r="G46" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="H46" s="77" t="n">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="I46" s="77" t="n">
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="J46" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K46" s="77" t="n">
+        <x:v>84.5</x:v>
+      </x:c>
+      <x:c r="L46" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M46" s="77" t="n"/>
       <x:c r="N46" t="n">
-        <x:v>1.99</x:v>
+        <x:v>199</x:v>
+      </x:c>
+      <x:c r="O46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P46" t="n">
+        <x:v>84.5</x:v>
       </x:c>
       <x:c r="Q46">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R46">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S46">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G46">
-        <x:v>79000</x:v>
-      </x:c>
-      <x:c r="O46">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P46">
-        <x:v>84500</x:v>
+      <x:c r="R46" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S46" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="47">
@@ -3543,42 +3489,42 @@
       </x:c>
       <x:c r="E47" s="77" t="n"/>
       <x:c r="F47" s="77" t="n"/>
-      <x:c r="H47" s="77">
-        <x:v>90000</x:v>
-      </x:c>
-      <x:c r="I47" s="77">
-        <x:v>180000</x:v>
-      </x:c>
-      <x:c r="J47" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K47" s="77">
-        <x:v>69500</x:v>
-      </x:c>
-      <x:c r="L47" s="77">
+      <x:c r="G47" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H47" s="77" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I47" s="77" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J47" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K47" s="77" t="n">
+        <x:v>69.5</x:v>
+      </x:c>
+      <x:c r="L47" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M47" s="77" t="n"/>
       <x:c r="N47" t="n">
-        <x:v>1.69</x:v>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="O47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P47" t="n">
+        <x:v>69.5</x:v>
       </x:c>
       <x:c r="Q47">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R47">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S47">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G47">
-        <x:v>90000</x:v>
-      </x:c>
-      <x:c r="O47">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P47">
-        <x:v>69500</x:v>
+      <x:c r="R47" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S47" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="48">
@@ -3596,42 +3542,42 @@
       </x:c>
       <x:c r="E48" s="77" t="n"/>
       <x:c r="F48" s="77" t="n"/>
-      <x:c r="H48" s="77">
-        <x:v>55000</x:v>
-      </x:c>
-      <x:c r="I48" s="77">
-        <x:v>191000</x:v>
-      </x:c>
-      <x:c r="J48" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K48" s="77">
-        <x:v>75700</x:v>
-      </x:c>
-      <x:c r="L48" s="77">
+      <x:c r="G48" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="H48" s="77" t="n">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="I48" s="77" t="n">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="J48" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K48" s="77" t="n">
+        <x:v>75.7</x:v>
+      </x:c>
+      <x:c r="L48" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M48" s="77" t="n"/>
       <x:c r="N48" t="n">
-        <x:v>2.21</x:v>
+        <x:v>221</x:v>
+      </x:c>
+      <x:c r="O48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P48" t="n">
+        <x:v>75.7</x:v>
       </x:c>
       <x:c r="Q48">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R48">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S48">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G48">
-        <x:v>55000</x:v>
-      </x:c>
-      <x:c r="O48">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P48">
-        <x:v>75700</x:v>
+      <x:c r="R48" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S48" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="49">
@@ -3649,42 +3595,42 @@
       </x:c>
       <x:c r="E49" s="77" t="n"/>
       <x:c r="F49" s="77" t="n"/>
-      <x:c r="H49" s="77">
-        <x:v>50500</x:v>
-      </x:c>
-      <x:c r="I49" s="77">
-        <x:v>160000</x:v>
-      </x:c>
-      <x:c r="J49" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K49" s="77">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="L49" s="77">
+      <x:c r="G49" t="n">
+        <x:v>50.5</x:v>
+      </x:c>
+      <x:c r="H49" s="77" t="n">
+        <x:v>50.5</x:v>
+      </x:c>
+      <x:c r="I49" s="77" t="n">
+        <x:v>160</x:v>
+      </x:c>
+      <x:c r="J49" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K49" s="77" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="L49" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M49" s="77" t="n"/>
       <x:c r="N49" t="n">
-        <x:v>2.19</x:v>
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="O49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P49" t="n">
+        <x:v>60</x:v>
       </x:c>
       <x:c r="Q49">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R49">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S49">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G49">
-        <x:v>50500</x:v>
-      </x:c>
-      <x:c r="O49">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P49">
-        <x:v>60000</x:v>
+      <x:c r="R49" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S49" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="50">
@@ -3702,42 +3648,42 @@
       </x:c>
       <x:c r="E50" s="77" t="n"/>
       <x:c r="F50" s="77" t="n"/>
-      <x:c r="H50" s="77">
-        <x:v>70943</x:v>
-      </x:c>
-      <x:c r="I50" s="77">
-        <x:v>150000</x:v>
-      </x:c>
-      <x:c r="J50" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K50" s="77">
-        <x:v>59400</x:v>
-      </x:c>
-      <x:c r="L50" s="77">
+      <x:c r="G50" t="n">
+        <x:v>70.943</x:v>
+      </x:c>
+      <x:c r="H50" s="77" t="n">
+        <x:v>70.943</x:v>
+      </x:c>
+      <x:c r="I50" s="77" t="n">
+        <x:v>150</x:v>
+      </x:c>
+      <x:c r="J50" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K50" s="77" t="n">
+        <x:v>59.4</x:v>
+      </x:c>
+      <x:c r="L50" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M50" s="77" t="n"/>
       <x:c r="N50" t="n">
-        <x:v>2.9</x:v>
+        <x:v>290</x:v>
+      </x:c>
+      <x:c r="O50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P50" t="n">
+        <x:v>59.4</x:v>
       </x:c>
       <x:c r="Q50">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R50">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S50">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G50">
-        <x:v>70943</x:v>
-      </x:c>
-      <x:c r="O50">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P50">
-        <x:v>59400</x:v>
+      <x:c r="R50" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S50" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="51">
@@ -3755,42 +3701,42 @@
       </x:c>
       <x:c r="E51" s="77" t="n"/>
       <x:c r="F51" s="77" t="n"/>
-      <x:c r="H51" s="77">
-        <x:v>57916</x:v>
-      </x:c>
-      <x:c r="I51" s="77">
-        <x:v>170000</x:v>
-      </x:c>
-      <x:c r="J51" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K51" s="77">
-        <x:v>63000</x:v>
-      </x:c>
-      <x:c r="L51" s="77">
+      <x:c r="G51" t="n">
+        <x:v>57.916</x:v>
+      </x:c>
+      <x:c r="H51" s="77" t="n">
+        <x:v>57.916</x:v>
+      </x:c>
+      <x:c r="I51" s="77" t="n">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="J51" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K51" s="77" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="L51" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M51" s="77" t="n"/>
       <x:c r="N51" t="n">
-        <x:v>2.25</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="O51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P51" t="n">
+        <x:v>63</x:v>
       </x:c>
       <x:c r="Q51">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R51">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S51">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G51">
-        <x:v>57916</x:v>
-      </x:c>
-      <x:c r="O51">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P51">
-        <x:v>63000</x:v>
+      <x:c r="R51" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S51" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="52">
@@ -3808,42 +3754,42 @@
       </x:c>
       <x:c r="E52" s="77" t="n"/>
       <x:c r="F52" s="77" t="n"/>
-      <x:c r="H52" s="77">
-        <x:v>114000</x:v>
-      </x:c>
-      <x:c r="I52" s="77">
-        <x:v>228000</x:v>
-      </x:c>
-      <x:c r="J52" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K52" s="77">
-        <x:v>109000</x:v>
-      </x:c>
-      <x:c r="L52" s="77">
+      <x:c r="G52" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="H52" s="77" t="n">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="I52" s="77" t="n">
+        <x:v>228</x:v>
+      </x:c>
+      <x:c r="J52" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K52" s="77" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="L52" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M52" s="77" t="n"/>
       <x:c r="N52" t="n">
-        <x:v>2.48</x:v>
+        <x:v>248</x:v>
+      </x:c>
+      <x:c r="O52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P52" t="n">
+        <x:v>109</x:v>
       </x:c>
       <x:c r="Q52">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R52">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S52">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G52">
-        <x:v>114000</x:v>
-      </x:c>
-      <x:c r="O52">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P52">
-        <x:v>109000</x:v>
+      <x:c r="R52" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S52" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="53">
@@ -3861,42 +3807,42 @@
       </x:c>
       <x:c r="E53" s="77" t="n"/>
       <x:c r="F53" s="77" t="n"/>
-      <x:c r="H53" s="77">
-        <x:v>109000</x:v>
-      </x:c>
-      <x:c r="I53" s="77">
-        <x:v>218000</x:v>
-      </x:c>
-      <x:c r="J53" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K53" s="77">
-        <x:v>94000</x:v>
-      </x:c>
-      <x:c r="L53" s="77">
+      <x:c r="G53" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="H53" s="77" t="n">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="I53" s="77" t="n">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="J53" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K53" s="77" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="L53" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M53" s="77" t="n"/>
       <x:c r="N53" t="n">
-        <x:v>2.18</x:v>
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="O53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P53" t="n">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="Q53">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R53">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S53">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G53">
-        <x:v>109000</x:v>
-      </x:c>
-      <x:c r="O53">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P53">
-        <x:v>94000</x:v>
+      <x:c r="R53" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S53" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="54">
@@ -3914,42 +3860,42 @@
       </x:c>
       <x:c r="E54" s="77" t="n"/>
       <x:c r="F54" s="77" t="n"/>
-      <x:c r="H54" s="77">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="I54" s="77">
-        <x:v>155000</x:v>
-      </x:c>
-      <x:c r="J54" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K54" s="77">
-        <x:v>77500</x:v>
-      </x:c>
-      <x:c r="L54" s="77">
+      <x:c r="G54" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="H54" s="77" t="n">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="I54" s="77" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J54" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K54" s="77" t="n">
+        <x:v>77.5</x:v>
+      </x:c>
+      <x:c r="L54" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M54" s="77" t="n"/>
       <x:c r="N54" t="n">
-        <x:v>1.85</x:v>
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="O54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P54" t="n">
+        <x:v>77.5</x:v>
       </x:c>
       <x:c r="Q54">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G54">
-        <x:v>60000</x:v>
-      </x:c>
-      <x:c r="O54">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P54">
-        <x:v>77500</x:v>
+      <x:c r="R54" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S54" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="55">
@@ -3967,42 +3913,42 @@
       </x:c>
       <x:c r="E55" s="77" t="n"/>
       <x:c r="F55" s="77" t="n"/>
-      <x:c r="H55" s="77">
-        <x:v>37000</x:v>
-      </x:c>
-      <x:c r="I55" s="77">
-        <x:v>156000</x:v>
-      </x:c>
-      <x:c r="J55" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K55" s="77">
-        <x:v>78000</x:v>
-      </x:c>
-      <x:c r="L55" s="77">
+      <x:c r="G55" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="H55" s="77" t="n">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="I55" s="77" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="J55" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K55" s="77" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="L55" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M55" s="77" t="n"/>
       <x:c r="N55" t="n">
-        <x:v>1.86</x:v>
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="O55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P55" t="n">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q55">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R55">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S55">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G55">
-        <x:v>37000</x:v>
-      </x:c>
-      <x:c r="O55">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P55">
-        <x:v>78000</x:v>
+      <x:c r="R55" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S55" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="56">
@@ -4020,42 +3966,42 @@
       </x:c>
       <x:c r="E56" s="77" t="n"/>
       <x:c r="F56" s="77" t="n"/>
-      <x:c r="H56" s="77">
-        <x:v>49000</x:v>
-      </x:c>
-      <x:c r="I56" s="77">
-        <x:v>156000</x:v>
-      </x:c>
-      <x:c r="J56" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K56" s="77">
-        <x:v>78000</x:v>
-      </x:c>
-      <x:c r="L56" s="77">
+      <x:c r="G56" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="H56" s="77" t="n">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I56" s="77" t="n">
+        <x:v>156</x:v>
+      </x:c>
+      <x:c r="J56" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K56" s="77" t="n">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="L56" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M56" s="77" t="n"/>
       <x:c r="N56" t="n">
-        <x:v>1.86</x:v>
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="O56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P56" t="n">
+        <x:v>78</x:v>
       </x:c>
       <x:c r="Q56">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R56">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S56">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G56">
-        <x:v>49000</x:v>
-      </x:c>
-      <x:c r="O56">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P56">
-        <x:v>78000</x:v>
+      <x:c r="R56" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S56" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="57">
@@ -4073,42 +4019,42 @@
       </x:c>
       <x:c r="E57" s="77" t="n"/>
       <x:c r="F57" s="77" t="n"/>
-      <x:c r="H57" s="77">
-        <x:v>132500</x:v>
-      </x:c>
-      <x:c r="I57" s="77">
-        <x:v>273000</x:v>
-      </x:c>
-      <x:c r="J57" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K57" s="77">
-        <x:v>136500</x:v>
-      </x:c>
-      <x:c r="L57" s="77">
+      <x:c r="G57" t="n">
+        <x:v>132.5</x:v>
+      </x:c>
+      <x:c r="H57" s="77" t="n">
+        <x:v>132.5</x:v>
+      </x:c>
+      <x:c r="I57" s="77" t="n">
+        <x:v>273</x:v>
+      </x:c>
+      <x:c r="J57" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K57" s="77" t="n">
+        <x:v>136.5</x:v>
+      </x:c>
+      <x:c r="L57" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M57" s="77" t="n"/>
       <x:c r="N57" t="n">
-        <x:v>3.03</x:v>
+        <x:v>303</x:v>
+      </x:c>
+      <x:c r="O57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P57" t="n">
+        <x:v>136.5</x:v>
       </x:c>
       <x:c r="Q57">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R57">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S57">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G57">
-        <x:v>132500</x:v>
-      </x:c>
-      <x:c r="O57">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P57">
-        <x:v>136500</x:v>
+      <x:c r="R57" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S57" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="58">
@@ -4126,42 +4072,42 @@
       </x:c>
       <x:c r="E58" s="77" t="n"/>
       <x:c r="F58" s="77" t="n"/>
-      <x:c r="H58" s="77">
-        <x:v>47000</x:v>
-      </x:c>
-      <x:c r="I58" s="77">
-        <x:v>162000</x:v>
-      </x:c>
-      <x:c r="J58" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K58" s="77">
-        <x:v>81000</x:v>
-      </x:c>
-      <x:c r="L58" s="77">
+      <x:c r="G58" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="H58" s="77" t="n">
+        <x:v>47</x:v>
+      </x:c>
+      <x:c r="I58" s="77" t="n">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="J58" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K58" s="77" t="n">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="L58" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M58" s="77" t="n"/>
       <x:c r="N58" t="n">
-        <x:v>1.92</x:v>
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="O58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P58" t="n">
+        <x:v>81</x:v>
       </x:c>
       <x:c r="Q58">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R58">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S58">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G58">
-        <x:v>47000</x:v>
-      </x:c>
-      <x:c r="O58">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P58">
-        <x:v>81000</x:v>
+      <x:c r="R58" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S58" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="59">
@@ -4179,42 +4125,42 @@
       </x:c>
       <x:c r="E59" s="77" t="n"/>
       <x:c r="F59" s="77" t="n"/>
-      <x:c r="H59" s="77">
-        <x:v>38500</x:v>
-      </x:c>
-      <x:c r="I59" s="77">
-        <x:v>180000</x:v>
-      </x:c>
-      <x:c r="J59" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K59" s="77">
-        <x:v>90000</x:v>
-      </x:c>
-      <x:c r="L59" s="77">
+      <x:c r="G59" t="n">
+        <x:v>38.5</x:v>
+      </x:c>
+      <x:c r="H59" s="77" t="n">
+        <x:v>38.5</x:v>
+      </x:c>
+      <x:c r="I59" s="77" t="n">
+        <x:v>180</x:v>
+      </x:c>
+      <x:c r="J59" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K59" s="77" t="n">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="L59" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M59" s="77" t="n"/>
       <x:c r="N59" t="n">
-        <x:v>2.1</x:v>
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="O59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P59" t="n">
+        <x:v>90</x:v>
       </x:c>
       <x:c r="Q59">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R59">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S59">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G59">
-        <x:v>38500</x:v>
-      </x:c>
-      <x:c r="O59">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P59">
-        <x:v>90000</x:v>
+      <x:c r="R59" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S59" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="60">
@@ -4232,42 +4178,42 @@
       </x:c>
       <x:c r="E60" s="77" t="n"/>
       <x:c r="F60" s="77" t="n"/>
-      <x:c r="H60" s="77">
-        <x:v>54500</x:v>
-      </x:c>
-      <x:c r="I60" s="77">
-        <x:v>195000</x:v>
-      </x:c>
-      <x:c r="J60" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K60" s="77">
-        <x:v>97500</x:v>
-      </x:c>
-      <x:c r="L60" s="77">
+      <x:c r="G60" t="n">
+        <x:v>54.5</x:v>
+      </x:c>
+      <x:c r="H60" s="77" t="n">
+        <x:v>54.5</x:v>
+      </x:c>
+      <x:c r="I60" s="77" t="n">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="J60" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K60" s="77" t="n">
+        <x:v>97.5</x:v>
+      </x:c>
+      <x:c r="L60" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M60" s="77" t="n"/>
       <x:c r="N60" t="n">
-        <x:v>2.25</x:v>
+        <x:v>225</x:v>
+      </x:c>
+      <x:c r="O60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P60" t="n">
+        <x:v>97.5</x:v>
       </x:c>
       <x:c r="Q60">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R60">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S60">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G60">
-        <x:v>54500</x:v>
-      </x:c>
-      <x:c r="O60">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P60">
-        <x:v>97500</x:v>
+      <x:c r="R60" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S60" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="61">
@@ -4285,42 +4231,42 @@
       </x:c>
       <x:c r="E61" s="77" t="n"/>
       <x:c r="F61" s="77" t="n"/>
-      <x:c r="H61" s="77">
-        <x:v>55500</x:v>
-      </x:c>
-      <x:c r="I61" s="77">
-        <x:v>155000</x:v>
-      </x:c>
-      <x:c r="J61" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K61" s="77">
-        <x:v>77500</x:v>
-      </x:c>
-      <x:c r="L61" s="77">
+      <x:c r="G61" t="n">
+        <x:v>55.5</x:v>
+      </x:c>
+      <x:c r="H61" s="77" t="n">
+        <x:v>55.5</x:v>
+      </x:c>
+      <x:c r="I61" s="77" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J61" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K61" s="77" t="n">
+        <x:v>77.5</x:v>
+      </x:c>
+      <x:c r="L61" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M61" s="77" t="n"/>
       <x:c r="N61" t="n">
-        <x:v>1.85</x:v>
+        <x:v>185</x:v>
+      </x:c>
+      <x:c r="O61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P61" t="n">
+        <x:v>77.5</x:v>
       </x:c>
       <x:c r="Q61">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R61">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S61">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G61">
-        <x:v>55500</x:v>
-      </x:c>
-      <x:c r="O61">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P61">
-        <x:v>77500</x:v>
+      <x:c r="R61" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S61" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="62">
@@ -4338,42 +4284,42 @@
       </x:c>
       <x:c r="E62" s="77" t="n"/>
       <x:c r="F62" s="77" t="n"/>
-      <x:c r="H62" s="77">
-        <x:v>43500</x:v>
-      </x:c>
-      <x:c r="I62" s="77">
-        <x:v>186000</x:v>
-      </x:c>
-      <x:c r="J62" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K62" s="77">
-        <x:v>93000</x:v>
-      </x:c>
-      <x:c r="L62" s="77">
+      <x:c r="G62" t="n">
+        <x:v>43.5</x:v>
+      </x:c>
+      <x:c r="H62" s="77" t="n">
+        <x:v>43.5</x:v>
+      </x:c>
+      <x:c r="I62" s="77" t="n">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="J62" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K62" s="77" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="L62" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M62" s="77" t="n"/>
       <x:c r="N62" t="n">
-        <x:v>2.16</x:v>
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="O62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P62" t="n">
+        <x:v>93</x:v>
       </x:c>
       <x:c r="Q62">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R62">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S62">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G62">
-        <x:v>43500</x:v>
-      </x:c>
-      <x:c r="O62">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P62">
-        <x:v>93000</x:v>
+      <x:c r="R62" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S62" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="63">
@@ -4391,42 +4337,42 @@
       </x:c>
       <x:c r="E63" s="77" t="n"/>
       <x:c r="F63" s="77" t="n"/>
-      <x:c r="H63" s="77">
-        <x:v>56500</x:v>
-      </x:c>
-      <x:c r="I63" s="77">
-        <x:v>171000</x:v>
-      </x:c>
-      <x:c r="J63" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K63" s="77">
-        <x:v>85500</x:v>
-      </x:c>
-      <x:c r="L63" s="77">
+      <x:c r="G63" t="n">
+        <x:v>56.5</x:v>
+      </x:c>
+      <x:c r="H63" s="77" t="n">
+        <x:v>56.5</x:v>
+      </x:c>
+      <x:c r="I63" s="77" t="n">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="J63" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K63" s="77" t="n">
+        <x:v>85.5</x:v>
+      </x:c>
+      <x:c r="L63" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M63" s="77" t="n"/>
       <x:c r="N63" t="n">
-        <x:v>2.01</x:v>
+        <x:v>201</x:v>
+      </x:c>
+      <x:c r="O63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P63" t="n">
+        <x:v>85.5</x:v>
       </x:c>
       <x:c r="Q63">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R63">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S63">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G63">
-        <x:v>56500</x:v>
-      </x:c>
-      <x:c r="O63">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P63">
-        <x:v>85500</x:v>
+      <x:c r="R63" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S63" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="64">
@@ -4444,42 +4390,42 @@
       </x:c>
       <x:c r="E64" s="77" t="n"/>
       <x:c r="F64" s="77" t="n"/>
-      <x:c r="H64" s="77">
-        <x:v>129000</x:v>
-      </x:c>
-      <x:c r="I64" s="77">
-        <x:v>258000</x:v>
-      </x:c>
-      <x:c r="J64" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K64" s="77">
-        <x:v>107500</x:v>
-      </x:c>
-      <x:c r="L64" s="77">
+      <x:c r="G64" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="H64" s="77" t="n">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="I64" s="77" t="n">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="J64" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K64" s="77" t="n">
+        <x:v>107.5</x:v>
+      </x:c>
+      <x:c r="L64" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M64" s="77" t="n"/>
       <x:c r="N64" t="n">
-        <x:v>2.45</x:v>
+        <x:v>245</x:v>
+      </x:c>
+      <x:c r="O64" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P64" t="n">
+        <x:v>107.5</x:v>
       </x:c>
       <x:c r="Q64">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R64">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S64">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G64">
-        <x:v>129000</x:v>
-      </x:c>
-      <x:c r="O64">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P64">
-        <x:v>107500</x:v>
+      <x:c r="R64" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S64" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="65">
@@ -4497,42 +4443,42 @@
       </x:c>
       <x:c r="E65" s="77" t="n"/>
       <x:c r="F65" s="77" t="n"/>
-      <x:c r="H65" s="77">
-        <x:v>99000</x:v>
-      </x:c>
-      <x:c r="I65" s="77">
-        <x:v>198000</x:v>
-      </x:c>
-      <x:c r="J65" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K65" s="77">
-        <x:v>94000</x:v>
-      </x:c>
-      <x:c r="L65" s="77">
+      <x:c r="G65" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="H65" s="77" t="n">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="I65" s="77" t="n">
+        <x:v>198</x:v>
+      </x:c>
+      <x:c r="J65" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K65" s="77" t="n">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="L65" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M65" s="77" t="n"/>
       <x:c r="N65" t="n">
-        <x:v>2.18</x:v>
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="O65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P65" t="n">
+        <x:v>94</x:v>
       </x:c>
       <x:c r="Q65">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R65">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S65">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G65">
-        <x:v>99000</x:v>
-      </x:c>
-      <x:c r="O65">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P65">
-        <x:v>94000</x:v>
+      <x:c r="R65" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S65" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="66">
@@ -4550,42 +4496,42 @@
       </x:c>
       <x:c r="E66" s="77" t="n"/>
       <x:c r="F66" s="77" t="n"/>
-      <x:c r="H66" s="77">
-        <x:v>106000</x:v>
-      </x:c>
-      <x:c r="I66" s="77">
-        <x:v>216000</x:v>
-      </x:c>
-      <x:c r="J66" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K66" s="77">
-        <x:v>108000</x:v>
-      </x:c>
-      <x:c r="L66" s="77">
+      <x:c r="G66" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H66" s="77" t="n">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I66" s="77" t="n">
+        <x:v>216</x:v>
+      </x:c>
+      <x:c r="J66" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K66" s="77" t="n">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="L66" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M66" s="77" t="n"/>
       <x:c r="N66" t="n">
-        <x:v>2.46</x:v>
+        <x:v>246</x:v>
+      </x:c>
+      <x:c r="O66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P66" t="n">
+        <x:v>108</x:v>
       </x:c>
       <x:c r="Q66">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R66">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S66">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G66">
-        <x:v>106000</x:v>
-      </x:c>
-      <x:c r="O66">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P66">
-        <x:v>108000</x:v>
+      <x:c r="R66" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S66" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="67">
@@ -4603,42 +4549,42 @@
       </x:c>
       <x:c r="E67" s="77" t="n"/>
       <x:c r="F67" s="77" t="n"/>
-      <x:c r="H67" s="77">
-        <x:v>63000</x:v>
-      </x:c>
-      <x:c r="I67" s="77">
-        <x:v>177000</x:v>
-      </x:c>
-      <x:c r="J67" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K67" s="77">
-        <x:v>88500</x:v>
-      </x:c>
-      <x:c r="L67" s="77">
+      <x:c r="G67" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="H67" s="77" t="n">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="I67" s="77" t="n">
+        <x:v>177</x:v>
+      </x:c>
+      <x:c r="J67" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K67" s="77" t="n">
+        <x:v>88.5</x:v>
+      </x:c>
+      <x:c r="L67" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M67" s="77" t="n"/>
       <x:c r="N67" t="n">
-        <x:v>2.07</x:v>
+        <x:v>207</x:v>
+      </x:c>
+      <x:c r="O67" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P67" t="n">
+        <x:v>88.5</x:v>
       </x:c>
       <x:c r="Q67">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R67">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S67">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G67">
-        <x:v>63000</x:v>
-      </x:c>
-      <x:c r="O67">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P67">
-        <x:v>88500</x:v>
+      <x:c r="R67" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S67" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="68">
@@ -4656,42 +4602,42 @@
       </x:c>
       <x:c r="E68" s="77" t="n"/>
       <x:c r="F68" s="77" t="n"/>
-      <x:c r="H68" s="77">
-        <x:v>52500</x:v>
-      </x:c>
-      <x:c r="I68" s="77">
-        <x:v>175000</x:v>
-      </x:c>
-      <x:c r="J68" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K68" s="77">
-        <x:v>87500</x:v>
-      </x:c>
-      <x:c r="L68" s="77">
+      <x:c r="G68" t="n">
+        <x:v>52.5</x:v>
+      </x:c>
+      <x:c r="H68" s="77" t="n">
+        <x:v>52.5</x:v>
+      </x:c>
+      <x:c r="I68" s="77" t="n">
+        <x:v>175</x:v>
+      </x:c>
+      <x:c r="J68" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K68" s="77" t="n">
+        <x:v>87.5</x:v>
+      </x:c>
+      <x:c r="L68" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M68" s="77" t="n"/>
       <x:c r="N68" t="n">
-        <x:v>2.05</x:v>
+        <x:v>205</x:v>
+      </x:c>
+      <x:c r="O68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P68" t="n">
+        <x:v>87.5</x:v>
       </x:c>
       <x:c r="Q68">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R68">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S68">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G68">
-        <x:v>52500</x:v>
-      </x:c>
-      <x:c r="O68">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P68">
-        <x:v>87500</x:v>
+      <x:c r="R68" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S68" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="69">
@@ -4709,42 +4655,42 @@
       </x:c>
       <x:c r="E69" s="77" t="n"/>
       <x:c r="F69" s="77" t="n"/>
-      <x:c r="H69" s="77">
-        <x:v>77500</x:v>
-      </x:c>
-      <x:c r="I69" s="77">
-        <x:v>155000</x:v>
-      </x:c>
-      <x:c r="J69" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K69" s="77">
-        <x:v>76500</x:v>
-      </x:c>
-      <x:c r="L69" s="77">
+      <x:c r="G69" t="n">
+        <x:v>77.5</x:v>
+      </x:c>
+      <x:c r="H69" s="77" t="n">
+        <x:v>77.5</x:v>
+      </x:c>
+      <x:c r="I69" s="77" t="n">
+        <x:v>155</x:v>
+      </x:c>
+      <x:c r="J69" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K69" s="77" t="n">
+        <x:v>76.5</x:v>
+      </x:c>
+      <x:c r="L69" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M69" s="77" t="n"/>
       <x:c r="N69" t="n">
-        <x:v>1.83</x:v>
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="O69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P69" t="n">
+        <x:v>76.5</x:v>
       </x:c>
       <x:c r="Q69">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R69">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S69">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G69">
-        <x:v>77500</x:v>
-      </x:c>
-      <x:c r="O69">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P69">
-        <x:v>76500</x:v>
+      <x:c r="R69" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S69" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="70">
@@ -4762,42 +4708,42 @@
       </x:c>
       <x:c r="E70" s="77" t="n"/>
       <x:c r="F70" s="77" t="n"/>
-      <x:c r="H70" s="77">
-        <x:v>56500</x:v>
-      </x:c>
-      <x:c r="I70" s="77">
-        <x:v>183000</x:v>
-      </x:c>
-      <x:c r="J70" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K70" s="77">
-        <x:v>91500</x:v>
-      </x:c>
-      <x:c r="L70" s="77">
+      <x:c r="G70" t="n">
+        <x:v>56.5</x:v>
+      </x:c>
+      <x:c r="H70" s="77" t="n">
+        <x:v>56.5</x:v>
+      </x:c>
+      <x:c r="I70" s="77" t="n">
+        <x:v>183</x:v>
+      </x:c>
+      <x:c r="J70" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K70" s="77" t="n">
+        <x:v>91.5</x:v>
+      </x:c>
+      <x:c r="L70" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M70" s="77" t="n"/>
       <x:c r="N70" t="n">
-        <x:v>2.13</x:v>
+        <x:v>213</x:v>
+      </x:c>
+      <x:c r="O70" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P70" t="n">
+        <x:v>91.5</x:v>
       </x:c>
       <x:c r="Q70">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R70">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S70">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G70">
-        <x:v>56500</x:v>
-      </x:c>
-      <x:c r="O70">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P70">
-        <x:v>91500</x:v>
+      <x:c r="R70" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S70" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="71">
@@ -4815,42 +4761,42 @@
       </x:c>
       <x:c r="E71" s="77" t="n"/>
       <x:c r="F71" s="77" t="n"/>
-      <x:c r="H71" s="77">
-        <x:v>60500</x:v>
-      </x:c>
-      <x:c r="I71" s="77">
-        <x:v>192000</x:v>
-      </x:c>
-      <x:c r="J71" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K71" s="77">
-        <x:v>96000</x:v>
-      </x:c>
-      <x:c r="L71" s="77">
+      <x:c r="G71" t="n">
+        <x:v>60.5</x:v>
+      </x:c>
+      <x:c r="H71" s="77" t="n">
+        <x:v>60.5</x:v>
+      </x:c>
+      <x:c r="I71" s="77" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="J71" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K71" s="77" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="L71" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M71" s="77" t="n"/>
       <x:c r="N71" t="n">
-        <x:v>2.22</x:v>
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="O71" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P71" t="n">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="Q71">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R71">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S71">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G71">
-        <x:v>60500</x:v>
-      </x:c>
-      <x:c r="O71">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P71">
-        <x:v>96000</x:v>
+      <x:c r="R71" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S71" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="72">
@@ -4868,42 +4814,42 @@
       </x:c>
       <x:c r="E72" s="77" t="n"/>
       <x:c r="F72" s="77" t="n"/>
-      <x:c r="H72" s="77">
-        <x:v>68500</x:v>
-      </x:c>
-      <x:c r="I72" s="77">
-        <x:v>139000</x:v>
-      </x:c>
-      <x:c r="J72" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K72" s="77">
-        <x:v>69500</x:v>
-      </x:c>
-      <x:c r="L72" s="77">
+      <x:c r="G72" t="n">
+        <x:v>68.5</x:v>
+      </x:c>
+      <x:c r="H72" s="77" t="n">
+        <x:v>68.5</x:v>
+      </x:c>
+      <x:c r="I72" s="77" t="n">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="J72" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K72" s="77" t="n">
+        <x:v>69.5</x:v>
+      </x:c>
+      <x:c r="L72" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M72" s="77" t="n"/>
       <x:c r="N72" t="n">
-        <x:v>1.69</x:v>
+        <x:v>169</x:v>
+      </x:c>
+      <x:c r="O72" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P72" t="n">
+        <x:v>69.5</x:v>
       </x:c>
       <x:c r="Q72">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R72">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S72">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G72">
-        <x:v>68500</x:v>
-      </x:c>
-      <x:c r="O72">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P72">
-        <x:v>69500</x:v>
+      <x:c r="R72" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S72" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="73">
@@ -4921,42 +4867,42 @@
       </x:c>
       <x:c r="E73" s="77" t="n"/>
       <x:c r="F73" s="77" t="n"/>
-      <x:c r="H73" s="77">
-        <x:v>59500</x:v>
-      </x:c>
-      <x:c r="I73" s="77">
-        <x:v>194000</x:v>
-      </x:c>
-      <x:c r="J73" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K73" s="77">
-        <x:v>97000</x:v>
-      </x:c>
-      <x:c r="L73" s="77">
+      <x:c r="G73" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="H73" s="77" t="n">
+        <x:v>59.5</x:v>
+      </x:c>
+      <x:c r="I73" s="77" t="n">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="J73" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K73" s="77" t="n">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="L73" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M73" s="77" t="n"/>
       <x:c r="N73" t="n">
-        <x:v>2.24</x:v>
+        <x:v>224</x:v>
+      </x:c>
+      <x:c r="O73" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P73" t="n">
+        <x:v>97</x:v>
       </x:c>
       <x:c r="Q73">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R73">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S73">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G73">
-        <x:v>59500</x:v>
-      </x:c>
-      <x:c r="O73">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P73">
-        <x:v>97000</x:v>
+      <x:c r="R73" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S73" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="74">
@@ -4974,42 +4920,42 @@
       </x:c>
       <x:c r="E74" s="77" t="n"/>
       <x:c r="F74" s="77" t="n"/>
-      <x:c r="H74" s="77">
-        <x:v>73000</x:v>
-      </x:c>
-      <x:c r="I74" s="77">
-        <x:v>176000</x:v>
-      </x:c>
-      <x:c r="J74" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K74" s="77">
-        <x:v>88000</x:v>
-      </x:c>
-      <x:c r="L74" s="77">
+      <x:c r="G74" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="H74" s="77" t="n">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="I74" s="77" t="n">
+        <x:v>176</x:v>
+      </x:c>
+      <x:c r="J74" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K74" s="77" t="n">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="L74" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M74" s="77" t="n"/>
       <x:c r="N74" t="n">
-        <x:v>2.06</x:v>
+        <x:v>206</x:v>
+      </x:c>
+      <x:c r="O74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P74" t="n">
+        <x:v>88</x:v>
       </x:c>
       <x:c r="Q74">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R74">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S74">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G74">
-        <x:v>73000</x:v>
-      </x:c>
-      <x:c r="O74">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P74">
-        <x:v>88000</x:v>
+      <x:c r="R74" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S74" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="75">
@@ -5027,42 +4973,42 @@
       </x:c>
       <x:c r="E75" s="77" t="n"/>
       <x:c r="F75" s="77" t="n"/>
-      <x:c r="H75" s="77">
-        <x:v>35500</x:v>
-      </x:c>
-      <x:c r="I75" s="77">
-        <x:v>184000</x:v>
-      </x:c>
-      <x:c r="J75" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K75" s="77">
-        <x:v>92000</x:v>
-      </x:c>
-      <x:c r="L75" s="77">
+      <x:c r="G75" t="n">
+        <x:v>35.5</x:v>
+      </x:c>
+      <x:c r="H75" s="77" t="n">
+        <x:v>35.5</x:v>
+      </x:c>
+      <x:c r="I75" s="77" t="n">
+        <x:v>184</x:v>
+      </x:c>
+      <x:c r="J75" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K75" s="77" t="n">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="L75" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M75" s="77" t="n"/>
       <x:c r="N75" t="n">
-        <x:v>2.14</x:v>
+        <x:v>214</x:v>
+      </x:c>
+      <x:c r="O75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P75" t="n">
+        <x:v>92</x:v>
       </x:c>
       <x:c r="Q75">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R75">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S75">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G75">
-        <x:v>35500</x:v>
-      </x:c>
-      <x:c r="O75">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P75">
-        <x:v>92000</x:v>
+      <x:c r="R75" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S75" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="76">
@@ -5080,42 +5026,42 @@
       </x:c>
       <x:c r="E76" s="77" t="n"/>
       <x:c r="F76" s="77" t="n"/>
-      <x:c r="H76" s="77">
-        <x:v>38500</x:v>
-      </x:c>
-      <x:c r="I76" s="77">
-        <x:v>151000</x:v>
-      </x:c>
-      <x:c r="J76" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K76" s="77">
-        <x:v>75500</x:v>
-      </x:c>
-      <x:c r="L76" s="77">
+      <x:c r="G76" t="n">
+        <x:v>38.5</x:v>
+      </x:c>
+      <x:c r="H76" s="77" t="n">
+        <x:v>38.5</x:v>
+      </x:c>
+      <x:c r="I76" s="77" t="n">
+        <x:v>151</x:v>
+      </x:c>
+      <x:c r="J76" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K76" s="77" t="n">
+        <x:v>75.5</x:v>
+      </x:c>
+      <x:c r="L76" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M76" s="77" t="n"/>
       <x:c r="N76" t="n">
-        <x:v>1.81</x:v>
+        <x:v>181</x:v>
+      </x:c>
+      <x:c r="O76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P76" t="n">
+        <x:v>75.5</x:v>
       </x:c>
       <x:c r="Q76">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R76">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S76">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G76">
-        <x:v>38500</x:v>
-      </x:c>
-      <x:c r="O76">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P76">
-        <x:v>75500</x:v>
+      <x:c r="R76" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S76" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="77">
@@ -5133,42 +5079,42 @@
       </x:c>
       <x:c r="E77" s="77" t="n"/>
       <x:c r="F77" s="77" t="n"/>
-      <x:c r="H77" s="77">
-        <x:v>77000</x:v>
-      </x:c>
-      <x:c r="I77" s="77">
-        <x:v>192000</x:v>
-      </x:c>
-      <x:c r="J77" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K77" s="77">
-        <x:v>96000</x:v>
-      </x:c>
-      <x:c r="L77" s="77">
+      <x:c r="G77" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="H77" s="77" t="n">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="I77" s="77" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="J77" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K77" s="77" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="L77" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M77" s="77" t="n"/>
       <x:c r="N77" t="n">
-        <x:v>2.22</x:v>
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="O77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P77" t="n">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="Q77">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G77">
-        <x:v>77000</x:v>
-      </x:c>
-      <x:c r="O77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P77">
-        <x:v>96000</x:v>
+      <x:c r="R77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S77" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="78">
@@ -5186,42 +5132,42 @@
       </x:c>
       <x:c r="E78" s="77" t="n"/>
       <x:c r="F78" s="77" t="n"/>
-      <x:c r="H78" s="77">
-        <x:v>93500</x:v>
-      </x:c>
-      <x:c r="I78" s="77">
-        <x:v>219000</x:v>
-      </x:c>
-      <x:c r="J78" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K78" s="77">
-        <x:v>109500</x:v>
-      </x:c>
-      <x:c r="L78" s="77">
+      <x:c r="G78" t="n">
+        <x:v>93.5</x:v>
+      </x:c>
+      <x:c r="H78" s="77" t="n">
+        <x:v>93.5</x:v>
+      </x:c>
+      <x:c r="I78" s="77" t="n">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="J78" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K78" s="77" t="n">
+        <x:v>109.5</x:v>
+      </x:c>
+      <x:c r="L78" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M78" s="77" t="n"/>
       <x:c r="N78" t="n">
-        <x:v>2.49</x:v>
+        <x:v>249</x:v>
+      </x:c>
+      <x:c r="O78" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P78" t="n">
+        <x:v>109.5</x:v>
       </x:c>
       <x:c r="Q78">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R78">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S78">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G78">
-        <x:v>93500</x:v>
-      </x:c>
-      <x:c r="O78">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P78">
-        <x:v>109500</x:v>
+      <x:c r="R78" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S78" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="79">
@@ -5239,42 +5185,42 @@
       </x:c>
       <x:c r="E79" s="77" t="n"/>
       <x:c r="F79" s="77" t="n"/>
-      <x:c r="H79" s="77">
-        <x:v>25000</x:v>
-      </x:c>
-      <x:c r="I79" s="77">
-        <x:v>122000</x:v>
-      </x:c>
-      <x:c r="J79" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K79" s="77">
-        <x:v>61000</x:v>
-      </x:c>
-      <x:c r="L79" s="77">
+      <x:c r="G79" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="H79" s="77" t="n">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I79" s="77" t="n">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="J79" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K79" s="77" t="n">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="L79" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M79" s="77" t="n"/>
       <x:c r="N79" t="n">
-        <x:v>1.52</x:v>
+        <x:v>152</x:v>
+      </x:c>
+      <x:c r="O79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P79" t="n">
+        <x:v>61</x:v>
       </x:c>
       <x:c r="Q79">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R79">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S79">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G79">
-        <x:v>25000</x:v>
-      </x:c>
-      <x:c r="O79">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P79">
-        <x:v>61000</x:v>
+      <x:c r="R79" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S79" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="80">
@@ -5292,42 +5238,42 @@
       </x:c>
       <x:c r="E80" s="77" t="n"/>
       <x:c r="F80" s="77" t="n"/>
-      <x:c r="H80" s="77">
-        <x:v>21000</x:v>
-      </x:c>
-      <x:c r="I80" s="77">
-        <x:v>100000</x:v>
-      </x:c>
-      <x:c r="J80" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K80" s="77">
-        <x:v>50000</x:v>
-      </x:c>
-      <x:c r="L80" s="77">
+      <x:c r="G80" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="H80" s="77" t="n">
+        <x:v>21</x:v>
+      </x:c>
+      <x:c r="I80" s="77" t="n">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="J80" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K80" s="77" t="n">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="L80" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M80" s="77" t="n"/>
       <x:c r="N80" t="n">
-        <x:v>1.3</x:v>
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="O80" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P80" t="n">
+        <x:v>50</x:v>
       </x:c>
       <x:c r="Q80">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R80">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S80">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G80">
-        <x:v>21000</x:v>
-      </x:c>
-      <x:c r="O80">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P80">
-        <x:v>50000</x:v>
+      <x:c r="R80" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S80" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="81">
@@ -5345,42 +5291,42 @@
       </x:c>
       <x:c r="E81" s="77" t="n"/>
       <x:c r="F81" s="77" t="n"/>
-      <x:c r="H81" s="77">
-        <x:v>71500</x:v>
-      </x:c>
-      <x:c r="I81" s="77">
-        <x:v>265000</x:v>
-      </x:c>
-      <x:c r="J81" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K81" s="77">
-        <x:v>132500</x:v>
-      </x:c>
-      <x:c r="L81" s="77">
+      <x:c r="G81" t="n">
+        <x:v>71.5</x:v>
+      </x:c>
+      <x:c r="H81" s="77" t="n">
+        <x:v>71.5</x:v>
+      </x:c>
+      <x:c r="I81" s="77" t="n">
+        <x:v>265</x:v>
+      </x:c>
+      <x:c r="J81" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K81" s="77" t="n">
+        <x:v>132.5</x:v>
+      </x:c>
+      <x:c r="L81" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M81" s="77" t="n"/>
       <x:c r="N81" t="n">
-        <x:v>2.95</x:v>
+        <x:v>295</x:v>
+      </x:c>
+      <x:c r="O81" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P81" t="n">
+        <x:v>132.5</x:v>
       </x:c>
       <x:c r="Q81">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R81">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S81">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G81">
-        <x:v>71500</x:v>
-      </x:c>
-      <x:c r="O81">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P81">
-        <x:v>132500</x:v>
+      <x:c r="R81" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S81" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="82">
@@ -5398,42 +5344,42 @@
       </x:c>
       <x:c r="E82" s="77" t="n"/>
       <x:c r="F82" s="77" t="n"/>
-      <x:c r="H82" s="77">
-        <x:v>175500</x:v>
-      </x:c>
-      <x:c r="I82" s="77">
-        <x:v>351000</x:v>
-      </x:c>
-      <x:c r="J82" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K82" s="77">
-        <x:v>119000</x:v>
-      </x:c>
-      <x:c r="L82" s="77">
+      <x:c r="G82" t="n">
+        <x:v>175.5</x:v>
+      </x:c>
+      <x:c r="H82" s="77" t="n">
+        <x:v>175.5</x:v>
+      </x:c>
+      <x:c r="I82" s="77" t="n">
+        <x:v>351</x:v>
+      </x:c>
+      <x:c r="J82" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K82" s="77" t="n">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="L82" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M82" s="77" t="n"/>
       <x:c r="N82" t="n">
-        <x:v>2.68</x:v>
+        <x:v>268</x:v>
+      </x:c>
+      <x:c r="O82" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P82" t="n">
+        <x:v>119</x:v>
       </x:c>
       <x:c r="Q82">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R82">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S82">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G82">
-        <x:v>175500</x:v>
-      </x:c>
-      <x:c r="O82">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P82">
-        <x:v>119000</x:v>
+      <x:c r="R82" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S82" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="83">
@@ -5451,42 +5397,42 @@
       </x:c>
       <x:c r="E83" s="77" t="n"/>
       <x:c r="F83" s="77" t="n"/>
-      <x:c r="H83" s="77">
-        <x:v>93000</x:v>
-      </x:c>
-      <x:c r="I83" s="77">
-        <x:v>192000</x:v>
-      </x:c>
-      <x:c r="J83" s="77">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="K83" s="77">
-        <x:v>96000</x:v>
-      </x:c>
-      <x:c r="L83" s="77">
+      <x:c r="G83" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H83" s="77" t="n">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="I83" s="77" t="n">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="J83" s="77" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="K83" s="77" t="n">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="L83" s="77" t="n">
         <x:v>0</x:v>
       </x:c>
       <x:c r="M83" s="77" t="n"/>
       <x:c r="N83" t="n">
-        <x:v>2.22</x:v>
+        <x:v>222</x:v>
+      </x:c>
+      <x:c r="O83" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="P83" t="n">
+        <x:v>96</x:v>
       </x:c>
       <x:c r="Q83">
         <x:v>0</x:v>
       </x:c>
-      <x:c r="R83">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="S83">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G83">
-        <x:v>93000</x:v>
-      </x:c>
-      <x:c r="O83">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="P83">
-        <x:v>96000</x:v>
+      <x:c r="R83" t="n">
+        <x:v>0</x:v>
+      </x:c>
+      <x:c r="S83" t="n">
+        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="84">
